--- a/research/traditional_assets/database/data/qatar/qatar_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_engineering_construction.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08455249726775262</v>
+        <v>0.08450844477048486</v>
       </c>
       <c r="C2">
-        <v>2657.378076881392</v>
+        <v>2634.0031511067</v>
       </c>
       <c r="D2">
-        <v>2551.778076881392</v>
+        <v>2554.682151106701</v>
       </c>
       <c r="E2">
-        <v>-885.0000000000001</v>
+        <v>-858.7210000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>26.279</v>
       </c>
       <c r="G2">
         <v>105.6</v>
@@ -1433,28 +1433,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.3218337</v>
       </c>
       <c r="N2">
-        <v>178.9888888888889</v>
+        <v>177.6670551888889</v>
       </c>
       <c r="O2">
-        <v>17.89888888888889</v>
+        <v>17.76670551888889</v>
       </c>
       <c r="P2">
-        <v>161.09</v>
+        <v>159.90034967</v>
       </c>
       <c r="Q2">
-        <v>189.99</v>
+        <v>188.80034967</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08455249726775262</v>
+        <v>0.08490479269745946</v>
       </c>
       <c r="T2">
-        <v>0.776741878503467</v>
+        <v>0.783803168308044</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>135.4095366829344</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08450844477048486</v>
+        <v>0.08446439227321711</v>
       </c>
       <c r="C3">
-        <v>2634.0031511067</v>
+        <v>2610.634842879284</v>
       </c>
       <c r="D3">
-        <v>2554.682151106701</v>
+        <v>2557.592842879284</v>
       </c>
       <c r="E3">
-        <v>-858.7210000000001</v>
+        <v>-832.4420000000001</v>
       </c>
       <c r="F3">
-        <v>26.279</v>
+        <v>52.558</v>
       </c>
       <c r="G3">
         <v>105.6</v>
@@ -1515,28 +1515,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M3">
-        <v>1.3218337</v>
+        <v>2.6436674</v>
       </c>
       <c r="N3">
-        <v>177.6670551888889</v>
+        <v>176.3452214888889</v>
       </c>
       <c r="O3">
-        <v>17.76670551888889</v>
+        <v>17.63452214888889</v>
       </c>
       <c r="P3">
-        <v>159.90034967</v>
+        <v>158.71069934</v>
       </c>
       <c r="Q3">
-        <v>188.80034967</v>
+        <v>187.61069934</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08490479269745946</v>
+        <v>0.08526427782981338</v>
       </c>
       <c r="T3">
-        <v>0.783803168308044</v>
+        <v>0.7910085660678163</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.4095366829344</v>
+        <v>67.70476834146719</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08446439227321711</v>
+        <v>0.08442033977594936</v>
       </c>
       <c r="C4">
-        <v>2610.634842879284</v>
+        <v>2587.273174844166</v>
       </c>
       <c r="D4">
-        <v>2557.592842879284</v>
+        <v>2560.510174844166</v>
       </c>
       <c r="E4">
-        <v>-832.4420000000001</v>
+        <v>-806.1630000000001</v>
       </c>
       <c r="F4">
-        <v>52.558</v>
+        <v>78.837</v>
       </c>
       <c r="G4">
         <v>105.6</v>
@@ -1597,28 +1597,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M4">
-        <v>2.6436674</v>
+        <v>3.9655011</v>
       </c>
       <c r="N4">
-        <v>176.3452214888889</v>
+        <v>175.0233877888889</v>
       </c>
       <c r="O4">
-        <v>17.63452214888889</v>
+        <v>17.50233877888889</v>
       </c>
       <c r="P4">
-        <v>158.71069934</v>
+        <v>157.52104901</v>
       </c>
       <c r="Q4">
-        <v>187.61069934</v>
+        <v>186.42104901</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08526427782981338</v>
+        <v>0.08563117502675191</v>
       </c>
       <c r="T4">
-        <v>0.7910085660678163</v>
+        <v>0.798362528729852</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.70476834146719</v>
+        <v>45.13651222764479</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08442033977594936</v>
+        <v>0.08437628727868161</v>
       </c>
       <c r="C5">
-        <v>2587.273174844166</v>
+        <v>2563.918169749805</v>
       </c>
       <c r="D5">
-        <v>2560.510174844166</v>
+        <v>2563.434169749805</v>
       </c>
       <c r="E5">
-        <v>-806.1630000000001</v>
+        <v>-779.8840000000001</v>
       </c>
       <c r="F5">
-        <v>78.837</v>
+        <v>105.116</v>
       </c>
       <c r="G5">
         <v>105.6</v>
@@ -1679,28 +1679,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M5">
-        <v>3.9655011</v>
+        <v>5.2873348</v>
       </c>
       <c r="N5">
-        <v>175.0233877888889</v>
+        <v>173.7015540888889</v>
       </c>
       <c r="O5">
-        <v>17.50233877888889</v>
+        <v>17.37015540888889</v>
       </c>
       <c r="P5">
-        <v>157.52104901</v>
+        <v>156.33139868</v>
       </c>
       <c r="Q5">
-        <v>186.42104901</v>
+        <v>185.23139868</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08563117502675191</v>
+        <v>0.08600571591529335</v>
       </c>
       <c r="T5">
-        <v>0.798362528729852</v>
+        <v>0.8058696989473471</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.13651222764479</v>
+        <v>33.85238417073359</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08437628727868161</v>
+        <v>0.08433223478141386</v>
       </c>
       <c r="C6">
-        <v>2563.918169749805</v>
+        <v>2540.569850448695</v>
       </c>
       <c r="D6">
-        <v>2563.434169749805</v>
+        <v>2566.364850448695</v>
       </c>
       <c r="E6">
-        <v>-779.8840000000001</v>
+        <v>-753.6050000000001</v>
       </c>
       <c r="F6">
-        <v>105.116</v>
+        <v>131.395</v>
       </c>
       <c r="G6">
         <v>105.6</v>
@@ -1761,28 +1761,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M6">
-        <v>5.2873348</v>
+        <v>6.6091685</v>
       </c>
       <c r="N6">
-        <v>173.7015540888889</v>
+        <v>172.3797203888889</v>
       </c>
       <c r="O6">
-        <v>17.37015540888889</v>
+        <v>17.23797203888889</v>
       </c>
       <c r="P6">
-        <v>156.33139868</v>
+        <v>155.14174835</v>
       </c>
       <c r="Q6">
-        <v>185.23139868</v>
+        <v>184.04174835</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08600571591529335</v>
+        <v>0.08638814187517248</v>
       </c>
       <c r="T6">
-        <v>0.8058696989473471</v>
+        <v>0.8135349148536312</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.85238417073359</v>
+        <v>27.08190733658687</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08433223478141386</v>
+        <v>0.08428818228414608</v>
       </c>
       <c r="C7">
-        <v>2540.569850448695</v>
+        <v>2517.228239897951</v>
       </c>
       <c r="D7">
-        <v>2566.364850448695</v>
+        <v>2569.302239897951</v>
       </c>
       <c r="E7">
-        <v>-753.6050000000001</v>
+        <v>-727.3260000000001</v>
       </c>
       <c r="F7">
-        <v>131.395</v>
+        <v>157.674</v>
       </c>
       <c r="G7">
         <v>105.6</v>
@@ -1843,28 +1843,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M7">
-        <v>6.6091685</v>
+        <v>7.9310022</v>
       </c>
       <c r="N7">
-        <v>172.3797203888889</v>
+        <v>171.0578866888889</v>
       </c>
       <c r="O7">
-        <v>17.23797203888889</v>
+        <v>17.10578866888889</v>
       </c>
       <c r="P7">
-        <v>155.14174835</v>
+        <v>153.95209802</v>
       </c>
       <c r="Q7">
-        <v>184.04174835</v>
+        <v>182.85209802</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08638814187517248</v>
+        <v>0.08677870455760223</v>
       </c>
       <c r="T7">
-        <v>0.8135349148536312</v>
+        <v>0.8213632204600492</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.08190733658687</v>
+        <v>22.5682561138224</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08428818228414608</v>
+        <v>0.08424412978687836</v>
       </c>
       <c r="C8">
-        <v>2517.228239897951</v>
+        <v>2493.89336115991</v>
       </c>
       <c r="D8">
-        <v>2569.302239897951</v>
+        <v>2572.246361159911</v>
       </c>
       <c r="E8">
-        <v>-727.3260000000001</v>
+        <v>-701.0470000000001</v>
       </c>
       <c r="F8">
-        <v>157.674</v>
+        <v>183.953</v>
       </c>
       <c r="G8">
         <v>105.6</v>
@@ -1925,28 +1925,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M8">
-        <v>7.9310022</v>
+        <v>9.252835899999999</v>
       </c>
       <c r="N8">
-        <v>171.0578866888889</v>
+        <v>169.7360529888889</v>
       </c>
       <c r="O8">
-        <v>17.10578866888889</v>
+        <v>16.97360529888889</v>
       </c>
       <c r="P8">
-        <v>153.95209802</v>
+        <v>152.76244769</v>
       </c>
       <c r="Q8">
-        <v>182.85209802</v>
+        <v>181.66244769</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08677870455760223</v>
+        <v>0.0871776664375036</v>
       </c>
       <c r="T8">
-        <v>0.8213632204600492</v>
+        <v>0.8293598767246695</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.5682561138224</v>
+        <v>19.34421952613348</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08424412978687836</v>
+        <v>0.0842000772896106</v>
       </c>
       <c r="C9">
-        <v>2493.89336115991</v>
+        <v>2470.565237402747</v>
       </c>
       <c r="D9">
-        <v>2572.246361159911</v>
+        <v>2575.197237402747</v>
       </c>
       <c r="E9">
-        <v>-701.047</v>
+        <v>-674.7680000000001</v>
       </c>
       <c r="F9">
-        <v>183.953</v>
+        <v>210.232</v>
       </c>
       <c r="G9">
         <v>105.6</v>
@@ -2007,28 +2007,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M9">
-        <v>9.252835900000001</v>
+        <v>10.5746696</v>
       </c>
       <c r="N9">
-        <v>169.7360529888889</v>
+        <v>168.4142192888889</v>
       </c>
       <c r="O9">
-        <v>16.97360529888889</v>
+        <v>16.84142192888889</v>
       </c>
       <c r="P9">
-        <v>152.76244769</v>
+        <v>151.57279736</v>
       </c>
       <c r="Q9">
-        <v>181.66244769</v>
+        <v>180.47279736</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0871776664375036</v>
+        <v>0.08758530140175064</v>
       </c>
       <c r="T9">
-        <v>0.8293598767246697</v>
+        <v>0.8375303733428687</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.34421952613348</v>
+        <v>16.9261920853668</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0842000772896106</v>
+        <v>0.08415602479234285</v>
       </c>
       <c r="C10">
-        <v>2470.565237402747</v>
+        <v>2447.243891901063</v>
       </c>
       <c r="D10">
-        <v>2575.197237402747</v>
+        <v>2578.154891901063</v>
       </c>
       <c r="E10">
-        <v>-674.7680000000001</v>
+        <v>-648.4890000000001</v>
       </c>
       <c r="F10">
-        <v>210.232</v>
+        <v>236.511</v>
       </c>
       <c r="G10">
         <v>105.6</v>
@@ -2089,28 +2089,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M10">
-        <v>10.5746696</v>
+        <v>11.8965033</v>
       </c>
       <c r="N10">
-        <v>168.4142192888889</v>
+        <v>167.0923855888889</v>
       </c>
       <c r="O10">
-        <v>16.84142192888889</v>
+        <v>16.70923855888889</v>
       </c>
       <c r="P10">
-        <v>151.57279736</v>
+        <v>150.38314703</v>
       </c>
       <c r="Q10">
-        <v>180.47279736</v>
+        <v>179.28314703</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08758530140175064</v>
+        <v>0.08800189537620093</v>
       </c>
       <c r="T10">
-        <v>0.8375303733428687</v>
+        <v>0.8458804413153139</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.9261920853668</v>
+        <v>15.0455040758816</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08415602479234285</v>
+        <v>0.0841119722950751</v>
       </c>
       <c r="C11">
-        <v>2447.243891901063</v>
+        <v>2423.929348036513</v>
       </c>
       <c r="D11">
-        <v>2578.154891901063</v>
+        <v>2581.119348036513</v>
       </c>
       <c r="E11">
-        <v>-648.4890000000001</v>
+        <v>-622.2100000000002</v>
       </c>
       <c r="F11">
-        <v>236.511</v>
+        <v>262.79</v>
       </c>
       <c r="G11">
         <v>105.6</v>
@@ -2171,28 +2171,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M11">
-        <v>11.8965033</v>
+        <v>13.218337</v>
       </c>
       <c r="N11">
-        <v>167.0923855888889</v>
+        <v>165.7705518888889</v>
       </c>
       <c r="O11">
-        <v>16.70923855888889</v>
+        <v>16.57705518888889</v>
       </c>
       <c r="P11">
-        <v>150.38314703</v>
+        <v>149.1934967</v>
       </c>
       <c r="Q11">
-        <v>179.28314703</v>
+        <v>178.0934967</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08800189537620093</v>
+        <v>0.08842774699452788</v>
       </c>
       <c r="T11">
-        <v>0.8458804413153139</v>
+        <v>0.8544160663538137</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.0455040758816</v>
+        <v>13.54095366829344</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0841119722950751</v>
+        <v>0.08421641979780735</v>
       </c>
       <c r="C12">
-        <v>2423.929348036513</v>
+        <v>2390.632737557056</v>
       </c>
       <c r="D12">
-        <v>2581.119348036513</v>
+        <v>2574.101737557056</v>
       </c>
       <c r="E12">
-        <v>-622.21</v>
+        <v>-595.931</v>
       </c>
       <c r="F12">
-        <v>262.79</v>
+        <v>289.069</v>
       </c>
       <c r="G12">
         <v>105.6</v>
@@ -2253,45 +2253,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M12">
-        <v>13.218337</v>
+        <v>14.9737742</v>
       </c>
       <c r="N12">
-        <v>165.7705518888889</v>
+        <v>164.0151146888889</v>
       </c>
       <c r="O12">
-        <v>16.57705518888889</v>
+        <v>16.40151146888889</v>
       </c>
       <c r="P12">
-        <v>149.1934967</v>
+        <v>147.61360322</v>
       </c>
       <c r="Q12">
-        <v>178.0934967</v>
+        <v>176.51360322</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08842774699452788</v>
+        <v>0.08886316831214308</v>
       </c>
       <c r="T12">
-        <v>0.8544160663538137</v>
+        <v>0.8631435031909312</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.54095366829344</v>
+        <v>11.95349191848297</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08421641979780735</v>
+        <v>0.08418586730053959</v>
       </c>
       <c r="C13">
-        <v>2390.632737557056</v>
+        <v>2366.402544626801</v>
       </c>
       <c r="D13">
-        <v>2574.101737557056</v>
+        <v>2576.150544626801</v>
       </c>
       <c r="E13">
-        <v>-595.931</v>
+        <v>-569.652</v>
       </c>
       <c r="F13">
-        <v>289.069</v>
+        <v>315.348</v>
       </c>
       <c r="G13">
         <v>105.6</v>
@@ -2335,28 +2335,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M13">
-        <v>14.9737742</v>
+        <v>16.3350264</v>
       </c>
       <c r="N13">
-        <v>164.0151146888889</v>
+        <v>162.6538624888889</v>
       </c>
       <c r="O13">
-        <v>16.40151146888889</v>
+        <v>16.26538624888889</v>
       </c>
       <c r="P13">
-        <v>147.61360322</v>
+        <v>146.38847624</v>
       </c>
       <c r="Q13">
-        <v>176.51360322</v>
+        <v>175.28847624</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08886316831214308</v>
+        <v>0.08930848556879499</v>
       </c>
       <c r="T13">
-        <v>0.8631435031909312</v>
+        <v>0.8720692908652562</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.95349191848297</v>
+        <v>10.95736759194273</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08418586730053959</v>
+        <v>0.08415531480327183</v>
       </c>
       <c r="C14">
-        <v>2366.402544626801</v>
+        <v>2342.175615712118</v>
       </c>
       <c r="D14">
-        <v>2576.150544626801</v>
+        <v>2578.202615712118</v>
       </c>
       <c r="E14">
-        <v>-569.652</v>
+        <v>-543.373</v>
       </c>
       <c r="F14">
-        <v>315.348</v>
+        <v>341.627</v>
       </c>
       <c r="G14">
         <v>105.6</v>
@@ -2417,28 +2417,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M14">
-        <v>16.3350264</v>
+        <v>17.6962786</v>
       </c>
       <c r="N14">
-        <v>162.6538624888889</v>
+        <v>161.2926102888889</v>
       </c>
       <c r="O14">
-        <v>16.26538624888889</v>
+        <v>16.12926102888889</v>
       </c>
       <c r="P14">
-        <v>146.38847624</v>
+        <v>145.16334926</v>
       </c>
       <c r="Q14">
-        <v>175.28847624</v>
+        <v>174.06334926</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08930848556879499</v>
+        <v>0.08976404000376073</v>
       </c>
       <c r="T14">
-        <v>0.8720692908652562</v>
+        <v>0.8812002690608297</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.95736759194273</v>
+        <v>10.11449316179329</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08415531480327183</v>
+        <v>0.08433896230600407</v>
       </c>
       <c r="C15">
-        <v>2342.175615712118</v>
+        <v>2303.610854924016</v>
       </c>
       <c r="D15">
-        <v>2578.202615712118</v>
+        <v>2565.916854924016</v>
       </c>
       <c r="E15">
-        <v>-543.373</v>
+        <v>-517.0940000000001</v>
       </c>
       <c r="F15">
-        <v>341.627</v>
+        <v>367.9060000000001</v>
       </c>
       <c r="G15">
         <v>105.6</v>
@@ -2499,45 +2499,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M15">
-        <v>17.6962786</v>
+        <v>19.682971</v>
       </c>
       <c r="N15">
-        <v>161.2926102888889</v>
+        <v>159.3059178888889</v>
       </c>
       <c r="O15">
-        <v>16.12926102888889</v>
+        <v>15.93059178888889</v>
       </c>
       <c r="P15">
-        <v>145.16334926</v>
+        <v>143.3753261</v>
       </c>
       <c r="Q15">
-        <v>174.06334926</v>
+        <v>172.2753261</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08976404000376073</v>
+        <v>0.09023018872791172</v>
       </c>
       <c r="T15">
-        <v>0.8812002690608297</v>
+        <v>0.8905435955865331</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.11449316179329</v>
+        <v>9.093591048266486</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08433896230600407</v>
+        <v>0.08432370980873634</v>
       </c>
       <c r="C16">
-        <v>2303.610854924016</v>
+        <v>2278.347765385736</v>
       </c>
       <c r="D16">
-        <v>2565.916854924016</v>
+        <v>2566.932765385736</v>
       </c>
       <c r="E16">
-        <v>-517.0940000000001</v>
+        <v>-490.8150000000001</v>
       </c>
       <c r="F16">
-        <v>367.9060000000001</v>
+        <v>394.1850000000001</v>
       </c>
       <c r="G16">
         <v>105.6</v>
@@ -2581,28 +2581,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M16">
-        <v>19.682971</v>
+        <v>21.0888975</v>
       </c>
       <c r="N16">
-        <v>159.3059178888889</v>
+        <v>157.8999913888889</v>
       </c>
       <c r="O16">
-        <v>15.93059178888889</v>
+        <v>15.78999913888889</v>
       </c>
       <c r="P16">
-        <v>143.3753261</v>
+        <v>142.10999225</v>
       </c>
       <c r="Q16">
-        <v>172.2753261</v>
+        <v>171.00999225</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09023018872791172</v>
+        <v>0.09070730565733687</v>
       </c>
       <c r="T16">
-        <v>0.8905435955865331</v>
+        <v>0.9001067650893119</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.093591048266486</v>
+        <v>8.487351645048722</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08432370980873632</v>
+        <v>0.08430845731146858</v>
       </c>
       <c r="C17">
-        <v>2278.347765385737</v>
+        <v>2253.085480614651</v>
       </c>
       <c r="D17">
-        <v>2566.932765385737</v>
+        <v>2567.949480614651</v>
       </c>
       <c r="E17">
-        <v>-490.8150000000001</v>
+        <v>-464.5360000000001</v>
       </c>
       <c r="F17">
-        <v>394.185</v>
+        <v>420.464</v>
       </c>
       <c r="G17">
         <v>105.6</v>
@@ -2663,28 +2663,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M17">
-        <v>21.0888975</v>
+        <v>22.494824</v>
       </c>
       <c r="N17">
-        <v>157.8999913888889</v>
+        <v>156.4940648888889</v>
       </c>
       <c r="O17">
-        <v>15.78999913888889</v>
+        <v>15.64940648888889</v>
       </c>
       <c r="P17">
-        <v>142.10999225</v>
+        <v>140.8446584</v>
       </c>
       <c r="Q17">
-        <v>171.00999225</v>
+        <v>169.7446584</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09070730565733687</v>
+        <v>0.09119578251365307</v>
       </c>
       <c r="T17">
-        <v>0.9001067650893119</v>
+        <v>0.9098976291040614</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.487351645048722</v>
+        <v>7.956892167233177</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08430845731146858</v>
+        <v>0.08441560481420084</v>
       </c>
       <c r="C18">
-        <v>2253.085480614651</v>
+        <v>2219.68113905094</v>
       </c>
       <c r="D18">
-        <v>2567.949480614651</v>
+        <v>2560.82413905094</v>
       </c>
       <c r="E18">
-        <v>-464.5360000000001</v>
+        <v>-438.2570000000001</v>
       </c>
       <c r="F18">
-        <v>420.464</v>
+        <v>446.7430000000001</v>
       </c>
       <c r="G18">
         <v>105.6</v>
@@ -2745,45 +2745,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M18">
-        <v>22.494824</v>
+        <v>24.2581449</v>
       </c>
       <c r="N18">
-        <v>156.4940648888889</v>
+        <v>154.7307439888889</v>
       </c>
       <c r="O18">
-        <v>15.64940648888889</v>
+        <v>15.47307439888889</v>
       </c>
       <c r="P18">
-        <v>140.8446584</v>
+        <v>139.25766959</v>
       </c>
       <c r="Q18">
-        <v>169.7446584</v>
+        <v>168.15766959</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09119578251365307</v>
+        <v>0.09169602989662751</v>
       </c>
       <c r="T18">
-        <v>0.9098976291040614</v>
+        <v>0.9199244175529013</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.956892167233177</v>
+        <v>7.378506873742388</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08441560481420084</v>
+        <v>0.08440755231693307</v>
       </c>
       <c r="C19">
-        <v>2219.68113905094</v>
+        <v>2193.93625810655</v>
       </c>
       <c r="D19">
-        <v>2560.82413905094</v>
+        <v>2561.35825810655</v>
       </c>
       <c r="E19">
-        <v>-438.2570000000001</v>
+        <v>-411.9780000000001</v>
       </c>
       <c r="F19">
-        <v>446.7430000000001</v>
+        <v>473.022</v>
       </c>
       <c r="G19">
         <v>105.6</v>
@@ -2827,28 +2827,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M19">
-        <v>24.2581449</v>
+        <v>25.6850946</v>
       </c>
       <c r="N19">
-        <v>154.7307439888889</v>
+        <v>153.3037942888889</v>
       </c>
       <c r="O19">
-        <v>15.47307439888889</v>
+        <v>15.33037942888889</v>
       </c>
       <c r="P19">
-        <v>139.25766959</v>
+        <v>137.97341486</v>
       </c>
       <c r="Q19">
-        <v>168.15766959</v>
+        <v>166.87341486</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09169602989662751</v>
+        <v>0.09220847843528424</v>
       </c>
       <c r="T19">
-        <v>0.9199244175529013</v>
+        <v>0.9301957618175666</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.378506873742388</v>
+        <v>6.968589825201144</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08440755231693307</v>
+        <v>0.08439949981966532</v>
       </c>
       <c r="C20">
-        <v>2193.93625810655</v>
+        <v>2168.191600014385</v>
       </c>
       <c r="D20">
-        <v>2561.35825810655</v>
+        <v>2561.892600014385</v>
       </c>
       <c r="E20">
-        <v>-411.9780000000001</v>
+        <v>-385.6990000000001</v>
       </c>
       <c r="F20">
-        <v>473.022</v>
+        <v>499.301</v>
       </c>
       <c r="G20">
         <v>105.6</v>
@@ -2909,28 +2909,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M20">
-        <v>25.6850946</v>
+        <v>27.1120443</v>
       </c>
       <c r="N20">
-        <v>153.3037942888889</v>
+        <v>151.8768445888889</v>
       </c>
       <c r="O20">
-        <v>15.33037942888889</v>
+        <v>15.18768445888889</v>
       </c>
       <c r="P20">
-        <v>137.97341486</v>
+        <v>136.68916013</v>
       </c>
       <c r="Q20">
-        <v>166.87341486</v>
+        <v>165.58916013</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09220847843528424</v>
+        <v>0.09273358002427817</v>
       </c>
       <c r="T20">
-        <v>0.9301957618175666</v>
+        <v>0.9407207195208656</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.968589825201144</v>
+        <v>6.601821939664242</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08439949981966532</v>
+        <v>0.08439144732239758</v>
       </c>
       <c r="C21">
-        <v>2168.191600014385</v>
+        <v>2142.447164913947</v>
       </c>
       <c r="D21">
-        <v>2561.892600014385</v>
+        <v>2562.427164913947</v>
       </c>
       <c r="E21">
-        <v>-385.6990000000001</v>
+        <v>-359.4200000000001</v>
       </c>
       <c r="F21">
-        <v>499.301</v>
+        <v>525.58</v>
       </c>
       <c r="G21">
         <v>105.6</v>
@@ -2991,28 +2991,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M21">
-        <v>27.1120443</v>
+        <v>28.538994</v>
       </c>
       <c r="N21">
-        <v>151.8768445888889</v>
+        <v>150.4498948888889</v>
       </c>
       <c r="O21">
-        <v>15.18768445888889</v>
+        <v>15.04498948888889</v>
       </c>
       <c r="P21">
-        <v>136.68916013</v>
+        <v>135.4049054</v>
       </c>
       <c r="Q21">
-        <v>165.58916013</v>
+        <v>164.3049054</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09273358002427817</v>
+        <v>0.09327180915299696</v>
       </c>
       <c r="T21">
-        <v>0.9407207195208656</v>
+        <v>0.9515088011667471</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.601821939664242</v>
+        <v>6.271730842681031</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08439144732239758</v>
+        <v>0.08457239482512982</v>
       </c>
       <c r="C22">
-        <v>2142.447164913947</v>
+        <v>2104.209533044143</v>
       </c>
       <c r="D22">
-        <v>2562.427164913947</v>
+        <v>2550.468533044143</v>
       </c>
       <c r="E22">
-        <v>-359.4200000000001</v>
+        <v>-333.1410000000001</v>
       </c>
       <c r="F22">
-        <v>525.58</v>
+        <v>551.859</v>
       </c>
       <c r="G22">
         <v>105.6</v>
@@ -3073,45 +3073,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M22">
-        <v>28.538994</v>
+        <v>30.5178027</v>
       </c>
       <c r="N22">
-        <v>150.4498948888889</v>
+        <v>148.4710861888889</v>
       </c>
       <c r="O22">
-        <v>15.04498948888889</v>
+        <v>14.84710861888889</v>
       </c>
       <c r="P22">
-        <v>135.4049054</v>
+        <v>133.62397757</v>
       </c>
       <c r="Q22">
-        <v>164.3049054</v>
+        <v>162.52397757</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09327180915299696</v>
+        <v>0.09382366433560735</v>
       </c>
       <c r="T22">
-        <v>0.9515088011667471</v>
+        <v>0.9625699988036635</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.271730842681031</v>
+        <v>5.865064750840952</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08457239482512981</v>
+        <v>0.08457334232786207</v>
       </c>
       <c r="C23">
-        <v>2104.209533044144</v>
+        <v>2077.868207338943</v>
       </c>
       <c r="D23">
-        <v>2550.468533044144</v>
+        <v>2550.406207338943</v>
       </c>
       <c r="E23">
-        <v>-333.1410000000001</v>
+        <v>-306.8620000000001</v>
       </c>
       <c r="F23">
-        <v>551.859</v>
+        <v>578.138</v>
       </c>
       <c r="G23">
         <v>105.6</v>
@@ -3155,28 +3155,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M23">
-        <v>30.5178027</v>
+        <v>31.9710314</v>
       </c>
       <c r="N23">
-        <v>148.4710861888889</v>
+        <v>147.0178574888889</v>
       </c>
       <c r="O23">
-        <v>14.84710861888889</v>
+        <v>14.70178574888889</v>
       </c>
       <c r="P23">
-        <v>133.62397757</v>
+        <v>132.31607174</v>
       </c>
       <c r="Q23">
-        <v>162.52397757</v>
+        <v>161.21607174</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09382366433560735</v>
+        <v>0.09438966965110521</v>
       </c>
       <c r="T23">
-        <v>0.9625699988036635</v>
+        <v>0.9739148168928086</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.865064750840952</v>
+        <v>5.59847089853</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08457334232786207</v>
+        <v>0.0845742898305943</v>
       </c>
       <c r="C24">
-        <v>2077.868207338943</v>
+        <v>2051.52688467977</v>
       </c>
       <c r="D24">
-        <v>2550.406207338943</v>
+        <v>2550.34388467977</v>
       </c>
       <c r="E24">
-        <v>-306.8620000000001</v>
+        <v>-280.5830000000001</v>
       </c>
       <c r="F24">
-        <v>578.138</v>
+        <v>604.417</v>
       </c>
       <c r="G24">
         <v>105.6</v>
@@ -3237,28 +3237,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M24">
-        <v>31.9710314</v>
+        <v>33.42426010000001</v>
       </c>
       <c r="N24">
-        <v>147.0178574888889</v>
+        <v>145.5646287888889</v>
       </c>
       <c r="O24">
-        <v>14.70178574888889</v>
+        <v>14.55646287888889</v>
       </c>
       <c r="P24">
-        <v>132.31607174</v>
+        <v>131.00816591</v>
       </c>
       <c r="Q24">
-        <v>161.21607174</v>
+        <v>159.90816591</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09438966965110521</v>
+        <v>0.09497037640336922</v>
       </c>
       <c r="T24">
-        <v>0.9739148168928086</v>
+        <v>0.9855543055816718</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.59847089853</v>
+        <v>5.355059120333044</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0845742898305943</v>
+        <v>0.08457523733332656</v>
       </c>
       <c r="C25">
-        <v>2051.52688467977</v>
+        <v>2025.1855650664</v>
       </c>
       <c r="D25">
-        <v>2550.34388467977</v>
+        <v>2550.2815650664</v>
       </c>
       <c r="E25">
-        <v>-280.5830000000001</v>
+        <v>-254.3040000000001</v>
       </c>
       <c r="F25">
-        <v>604.417</v>
+        <v>630.696</v>
       </c>
       <c r="G25">
         <v>105.6</v>
@@ -3319,28 +3319,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M25">
-        <v>33.42426010000001</v>
+        <v>34.8774888</v>
       </c>
       <c r="N25">
-        <v>145.5646287888889</v>
+        <v>144.1114000888889</v>
       </c>
       <c r="O25">
-        <v>14.55646287888889</v>
+        <v>14.41114000888889</v>
       </c>
       <c r="P25">
-        <v>131.00816591</v>
+        <v>129.70026008</v>
       </c>
       <c r="Q25">
-        <v>159.90816591</v>
+        <v>158.60026008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09497037640336922</v>
+        <v>0.09556636491227177</v>
       </c>
       <c r="T25">
-        <v>0.9855543055816718</v>
+        <v>0.9975000966044524</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.355059120333044</v>
+        <v>5.131931656985834</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08457523733332656</v>
+        <v>0.0845761848360588</v>
       </c>
       <c r="C26">
-        <v>2025.1855650664</v>
+        <v>1998.844248498613</v>
       </c>
       <c r="D26">
-        <v>2550.2815650664</v>
+        <v>2550.219248498613</v>
       </c>
       <c r="E26">
-        <v>-254.3040000000001</v>
+        <v>-228.0250000000001</v>
       </c>
       <c r="F26">
-        <v>630.696</v>
+        <v>656.975</v>
       </c>
       <c r="G26">
         <v>105.6</v>
@@ -3401,28 +3401,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M26">
-        <v>34.8774888</v>
+        <v>36.33071750000001</v>
       </c>
       <c r="N26">
-        <v>144.1114000888889</v>
+        <v>142.6581713888889</v>
       </c>
       <c r="O26">
-        <v>14.41114000888889</v>
+        <v>14.26581713888889</v>
       </c>
       <c r="P26">
-        <v>129.70026008</v>
+        <v>128.39235425</v>
       </c>
       <c r="Q26">
-        <v>158.60026008</v>
+        <v>157.29235425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09556636491227177</v>
+        <v>0.0961782464480784</v>
       </c>
       <c r="T26">
-        <v>0.9975000966044524</v>
+        <v>1.009764442054507</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.131931656985834</v>
+        <v>4.926654390706401</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0845761848360588</v>
+        <v>0.08457713233879105</v>
       </c>
       <c r="C27">
-        <v>1998.844248498613</v>
+        <v>1972.502934976182</v>
       </c>
       <c r="D27">
-        <v>2550.219248498613</v>
+        <v>2550.156934976182</v>
       </c>
       <c r="E27">
-        <v>-228.0250000000001</v>
+        <v>-201.7460000000001</v>
       </c>
       <c r="F27">
-        <v>656.975</v>
+        <v>683.254</v>
       </c>
       <c r="G27">
         <v>105.6</v>
@@ -3483,28 +3483,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M27">
-        <v>36.33071750000001</v>
+        <v>37.7839462</v>
       </c>
       <c r="N27">
-        <v>142.6581713888889</v>
+        <v>141.2049426888889</v>
       </c>
       <c r="O27">
-        <v>14.26581713888889</v>
+        <v>14.12049426888889</v>
       </c>
       <c r="P27">
-        <v>128.39235425</v>
+        <v>127.08444842</v>
       </c>
       <c r="Q27">
-        <v>157.29235425</v>
+        <v>155.98444842</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0961782464480784</v>
+        <v>0.09680666532269061</v>
       </c>
       <c r="T27">
-        <v>1.009764442054507</v>
+        <v>1.022360256300509</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.926654390706401</v>
+        <v>4.737167683371539</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08457713233879105</v>
+        <v>0.08457807984152331</v>
       </c>
       <c r="C28">
-        <v>1972.502934976182</v>
+        <v>1946.161624498885</v>
       </c>
       <c r="D28">
-        <v>2550.156934976182</v>
+        <v>2550.094624498885</v>
       </c>
       <c r="E28">
-        <v>-201.7460000000001</v>
+        <v>-175.4670000000001</v>
       </c>
       <c r="F28">
-        <v>683.254</v>
+        <v>709.533</v>
       </c>
       <c r="G28">
         <v>105.6</v>
@@ -3565,28 +3565,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M28">
-        <v>37.7839462</v>
+        <v>39.2371749</v>
       </c>
       <c r="N28">
-        <v>141.2049426888889</v>
+        <v>139.7517139888889</v>
       </c>
       <c r="O28">
-        <v>14.12049426888889</v>
+        <v>13.97517139888889</v>
       </c>
       <c r="P28">
-        <v>127.08444842</v>
+        <v>125.77654259</v>
       </c>
       <c r="Q28">
-        <v>155.98444842</v>
+        <v>154.67654259</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09680666532269061</v>
+        <v>0.09745230115277165</v>
       </c>
       <c r="T28">
-        <v>1.022360256300509</v>
+        <v>1.035301161347772</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.737167683371539</v>
+        <v>4.561717028431852</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08457807984152331</v>
+        <v>0.08520902734425555</v>
       </c>
       <c r="C29">
-        <v>1946.161624498885</v>
+        <v>1879.055028806067</v>
       </c>
       <c r="D29">
-        <v>2550.094624498885</v>
+        <v>2509.267028806067</v>
       </c>
       <c r="E29">
-        <v>-175.4670000000001</v>
+        <v>-149.188</v>
       </c>
       <c r="F29">
-        <v>709.533</v>
+        <v>735.8120000000001</v>
       </c>
       <c r="G29">
         <v>105.6</v>
@@ -3647,45 +3647,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M29">
-        <v>39.2371749</v>
+        <v>42.52993360000001</v>
       </c>
       <c r="N29">
-        <v>139.7517139888889</v>
+        <v>136.4589552888889</v>
       </c>
       <c r="O29">
-        <v>13.97517139888889</v>
+        <v>13.64589552888889</v>
       </c>
       <c r="P29">
-        <v>125.77654259</v>
+        <v>122.81305976</v>
       </c>
       <c r="Q29">
-        <v>154.67654259</v>
+        <v>151.71305976</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09745230115277165</v>
+        <v>0.09811587131146604</v>
       </c>
       <c r="T29">
-        <v>1.035301161347772</v>
+        <v>1.048601535979681</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.561717028431852</v>
+        <v>4.208539109708106</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08520902734425555</v>
+        <v>0.08523247484698779</v>
       </c>
       <c r="C30">
-        <v>1879.055028806067</v>
+        <v>1851.283957975054</v>
       </c>
       <c r="D30">
-        <v>2509.267028806067</v>
+        <v>2507.774957975054</v>
       </c>
       <c r="E30">
-        <v>-149.188</v>
+        <v>-122.909</v>
       </c>
       <c r="F30">
-        <v>735.8120000000001</v>
+        <v>762.0910000000001</v>
       </c>
       <c r="G30">
         <v>105.6</v>
@@ -3729,28 +3729,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M30">
-        <v>42.52993360000001</v>
+        <v>44.04885980000001</v>
       </c>
       <c r="N30">
-        <v>136.4589552888889</v>
+        <v>134.9400290888889</v>
       </c>
       <c r="O30">
-        <v>13.64589552888889</v>
+        <v>13.49400290888889</v>
       </c>
       <c r="P30">
-        <v>122.81305976</v>
+        <v>121.44602618</v>
       </c>
       <c r="Q30">
-        <v>151.71305976</v>
+        <v>150.34602618</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09811587131146604</v>
+        <v>0.09879813358730676</v>
       </c>
       <c r="T30">
-        <v>1.048601535979681</v>
+        <v>1.062276569051925</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.208539109708106</v>
+        <v>4.063417071442309</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08523247484698777</v>
+        <v>0.08620092234972003</v>
       </c>
       <c r="C31">
-        <v>1851.283957975055</v>
+        <v>1764.891271103194</v>
       </c>
       <c r="D31">
-        <v>2507.774957975055</v>
+        <v>2447.661271103194</v>
       </c>
       <c r="E31">
-        <v>-122.9090000000001</v>
+        <v>-96.63000000000011</v>
       </c>
       <c r="F31">
-        <v>762.091</v>
+        <v>788.37</v>
       </c>
       <c r="G31">
         <v>105.6</v>
@@ -3811,45 +3811,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M31">
-        <v>44.0488598</v>
+        <v>48.327081</v>
       </c>
       <c r="N31">
-        <v>134.9400290888889</v>
+        <v>130.6618078888889</v>
       </c>
       <c r="O31">
-        <v>13.49400290888889</v>
+        <v>13.06618078888889</v>
       </c>
       <c r="P31">
-        <v>121.44602618</v>
+        <v>117.5956271</v>
       </c>
       <c r="Q31">
-        <v>150.34602618</v>
+        <v>146.4956271</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09879813358730674</v>
+        <v>0.09949988907102862</v>
       </c>
       <c r="T31">
-        <v>1.062276569051924</v>
+        <v>1.076342317354804</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.063417071442309</v>
+        <v>3.703697496004132</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08620092234972003</v>
+        <v>0.08625586985245229</v>
       </c>
       <c r="C32">
-        <v>1764.891271103194</v>
+        <v>1735.287836976031</v>
       </c>
       <c r="D32">
-        <v>2447.661271103194</v>
+        <v>2444.336836976031</v>
       </c>
       <c r="E32">
-        <v>-96.63000000000011</v>
+        <v>-70.35100000000011</v>
       </c>
       <c r="F32">
-        <v>788.37</v>
+        <v>814.649</v>
       </c>
       <c r="G32">
         <v>105.6</v>
@@ -3893,28 +3893,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M32">
-        <v>48.327081</v>
+        <v>49.9379837</v>
       </c>
       <c r="N32">
-        <v>130.6618078888889</v>
+        <v>129.0509051888889</v>
       </c>
       <c r="O32">
-        <v>13.06618078888889</v>
+        <v>12.90509051888889</v>
       </c>
       <c r="P32">
-        <v>117.5956271</v>
+        <v>116.14581467</v>
       </c>
       <c r="Q32">
-        <v>146.4956271</v>
+        <v>145.04581467</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09949988907102862</v>
+        <v>0.1002219852934091</v>
       </c>
       <c r="T32">
-        <v>1.076342317354804</v>
+        <v>1.090815768507043</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.703697496004132</v>
+        <v>3.584223383229805</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08625586985245229</v>
+        <v>0.08711721735518453</v>
       </c>
       <c r="C33">
-        <v>1735.287836976031</v>
+        <v>1658.051304858937</v>
       </c>
       <c r="D33">
-        <v>2444.336836976031</v>
+        <v>2393.379304858937</v>
       </c>
       <c r="E33">
-        <v>-70.35100000000011</v>
+        <v>-44.07200000000012</v>
       </c>
       <c r="F33">
-        <v>814.649</v>
+        <v>840.928</v>
       </c>
       <c r="G33">
         <v>105.6</v>
@@ -3975,45 +3975,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M33">
-        <v>49.9379837</v>
+        <v>53.9034848</v>
       </c>
       <c r="N33">
-        <v>129.0509051888889</v>
+        <v>125.0854040888889</v>
       </c>
       <c r="O33">
-        <v>12.90509051888889</v>
+        <v>12.50854040888889</v>
       </c>
       <c r="P33">
-        <v>116.14581467</v>
+        <v>112.57686368</v>
       </c>
       <c r="Q33">
-        <v>145.04581467</v>
+        <v>141.47686368</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1002219852934091</v>
+        <v>0.1009653196399773</v>
       </c>
       <c r="T33">
-        <v>1.090815768507043</v>
+        <v>1.105714909399053</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.1</v>
       </c>
       <c r="W33">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.584223383229805</v>
+        <v>3.32054392314333</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08711721735518453</v>
+        <v>0.08719736485791678</v>
       </c>
       <c r="C34">
-        <v>1658.051304858937</v>
+        <v>1627.138595079731</v>
       </c>
       <c r="D34">
-        <v>2393.379304858937</v>
+        <v>2388.745595079732</v>
       </c>
       <c r="E34">
-        <v>-44.07200000000012</v>
+        <v>-17.79300000000001</v>
       </c>
       <c r="F34">
-        <v>840.928</v>
+        <v>867.2070000000001</v>
       </c>
       <c r="G34">
         <v>105.6</v>
@@ -4057,28 +4057,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M34">
-        <v>53.9034848</v>
+        <v>55.58796870000001</v>
       </c>
       <c r="N34">
-        <v>125.0854040888889</v>
+        <v>123.4009201888889</v>
       </c>
       <c r="O34">
-        <v>12.50854040888889</v>
+        <v>12.34009201888889</v>
       </c>
       <c r="P34">
-        <v>112.57686368</v>
+        <v>111.06082817</v>
       </c>
       <c r="Q34">
-        <v>141.47686368</v>
+        <v>139.96082817</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1009653196399773</v>
+        <v>0.1017308430715176</v>
       </c>
       <c r="T34">
-        <v>1.105714909399053</v>
+        <v>1.121058800765452</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.32054392314333</v>
+        <v>3.219921380017774</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08719736485791678</v>
+        <v>0.08727751236064901</v>
       </c>
       <c r="C35">
-        <v>1627.138595079731</v>
+        <v>1596.243792848306</v>
       </c>
       <c r="D35">
-        <v>2388.745595079732</v>
+        <v>2384.129792848306</v>
       </c>
       <c r="E35">
-        <v>-17.79300000000001</v>
+        <v>8.48599999999999</v>
       </c>
       <c r="F35">
-        <v>867.2070000000001</v>
+        <v>893.4860000000001</v>
       </c>
       <c r="G35">
         <v>105.6</v>
@@ -4139,28 +4139,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M35">
-        <v>55.58796870000001</v>
+        <v>57.27245260000001</v>
       </c>
       <c r="N35">
-        <v>123.4009201888889</v>
+        <v>121.7164362888889</v>
       </c>
       <c r="O35">
-        <v>12.34009201888889</v>
+        <v>12.17164362888889</v>
       </c>
       <c r="P35">
-        <v>111.06082817</v>
+        <v>109.54479266</v>
       </c>
       <c r="Q35">
-        <v>139.96082817</v>
+        <v>138.44479266</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017308430715176</v>
+        <v>0.1025195641828016</v>
       </c>
       <c r="T35">
-        <v>1.121058800765452</v>
+        <v>1.136867658536893</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.219921380017774</v>
+        <v>3.125217810017252</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08727751236064901</v>
+        <v>0.08735765986338126</v>
       </c>
       <c r="C36">
-        <v>1596.243792848306</v>
+        <v>1565.366794555945</v>
       </c>
       <c r="D36">
-        <v>2384.129792848306</v>
+        <v>2379.531794555945</v>
       </c>
       <c r="E36">
-        <v>8.48599999999999</v>
+        <v>34.76499999999999</v>
       </c>
       <c r="F36">
-        <v>893.4860000000001</v>
+        <v>919.7650000000001</v>
       </c>
       <c r="G36">
         <v>105.6</v>
@@ -4221,28 +4221,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M36">
-        <v>57.27245260000001</v>
+        <v>58.95693650000001</v>
       </c>
       <c r="N36">
-        <v>121.7164362888889</v>
+        <v>120.0319523888889</v>
       </c>
       <c r="O36">
-        <v>12.17164362888889</v>
+        <v>12.00319523888889</v>
       </c>
       <c r="P36">
-        <v>109.54479266</v>
+        <v>108.02875715</v>
       </c>
       <c r="Q36">
-        <v>138.44479266</v>
+        <v>136.92875715</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1025195641828016</v>
+        <v>0.1033325536359712</v>
       </c>
       <c r="T36">
-        <v>1.136867658536893</v>
+        <v>1.153162942701301</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.125217810017252</v>
+        <v>3.035925872588187</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08735765986338126</v>
+        <v>0.08996500736611351</v>
       </c>
       <c r="C37">
-        <v>1565.366794555945</v>
+        <v>1398.608563322582</v>
       </c>
       <c r="D37">
-        <v>2379.531794555945</v>
+        <v>2239.052563322582</v>
       </c>
       <c r="E37">
-        <v>34.76499999999999</v>
+        <v>61.04399999999998</v>
       </c>
       <c r="F37">
-        <v>919.7650000000001</v>
+        <v>946.0440000000001</v>
       </c>
       <c r="G37">
         <v>105.6</v>
@@ -4303,45 +4303,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M37">
-        <v>58.95693650000001</v>
+        <v>68.02056360000002</v>
       </c>
       <c r="N37">
-        <v>120.0319523888889</v>
+        <v>110.9683252888889</v>
       </c>
       <c r="O37">
-        <v>12.00319523888889</v>
+        <v>11.09683252888889</v>
       </c>
       <c r="P37">
-        <v>108.02875715</v>
+        <v>99.87149275999998</v>
       </c>
       <c r="Q37">
-        <v>136.92875715</v>
+        <v>128.77149276</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1033325536359712</v>
+        <v>0.1041709490095524</v>
       </c>
       <c r="T37">
-        <v>1.153162942701301</v>
+        <v>1.169967454495847</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.035925872588187</v>
+        <v>2.631393793521712</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08996500736611351</v>
+        <v>0.09011535486884575</v>
       </c>
       <c r="C38">
-        <v>1398.608563322582</v>
+        <v>1364.733190408993</v>
       </c>
       <c r="D38">
-        <v>2239.052563322582</v>
+        <v>2231.456190408993</v>
       </c>
       <c r="E38">
-        <v>61.04399999999987</v>
+        <v>87.32299999999987</v>
       </c>
       <c r="F38">
-        <v>946.044</v>
+        <v>972.323</v>
       </c>
       <c r="G38">
         <v>105.6</v>
@@ -4385,28 +4385,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M38">
-        <v>68.0205636</v>
+        <v>69.91002370000001</v>
       </c>
       <c r="N38">
-        <v>110.9683252888889</v>
+        <v>109.0788651888889</v>
       </c>
       <c r="O38">
-        <v>11.09683252888889</v>
+        <v>10.90788651888889</v>
       </c>
       <c r="P38">
-        <v>99.87149276</v>
+        <v>98.17097866999998</v>
       </c>
       <c r="Q38">
-        <v>128.77149276</v>
+        <v>127.07097867</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1041709490095524</v>
+        <v>0.105035960109279</v>
       </c>
       <c r="T38">
-        <v>1.169967454495847</v>
+        <v>1.187305442855299</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.631393793521712</v>
+        <v>2.560275042345449</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09011535486884575</v>
+        <v>0.09159950237157803</v>
       </c>
       <c r="C39">
-        <v>1364.733190408993</v>
+        <v>1266.143139830697</v>
       </c>
       <c r="D39">
-        <v>2231.456190408993</v>
+        <v>2159.145139830697</v>
       </c>
       <c r="E39">
-        <v>87.32299999999987</v>
+        <v>113.602</v>
       </c>
       <c r="F39">
-        <v>972.323</v>
+        <v>998.6020000000001</v>
       </c>
       <c r="G39">
         <v>105.6</v>
@@ -4467,45 +4467,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M39">
-        <v>69.91002370000001</v>
+        <v>75.69403160000002</v>
       </c>
       <c r="N39">
-        <v>109.0788651888889</v>
+        <v>103.2948572888889</v>
       </c>
       <c r="O39">
-        <v>10.90788651888889</v>
+        <v>10.32948572888889</v>
       </c>
       <c r="P39">
-        <v>98.17097866999998</v>
+        <v>92.96537155999998</v>
       </c>
       <c r="Q39">
-        <v>127.07097867</v>
+        <v>121.86537156</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.105035960109279</v>
+        <v>0.1059288747928678</v>
       </c>
       <c r="T39">
-        <v>1.187305442855299</v>
+        <v>1.205202721161831</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.560275042345449</v>
+        <v>2.364636750156783</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09159950237157803</v>
+        <v>0.09178494987431025</v>
       </c>
       <c r="C40">
-        <v>1266.143139830697</v>
+        <v>1231.156767629304</v>
       </c>
       <c r="D40">
-        <v>2159.145139830697</v>
+        <v>2150.437767629304</v>
       </c>
       <c r="E40">
-        <v>113.602</v>
+        <v>139.881</v>
       </c>
       <c r="F40">
-        <v>998.6020000000001</v>
+        <v>1024.881</v>
       </c>
       <c r="G40">
         <v>105.6</v>
@@ -4549,28 +4549,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M40">
-        <v>75.69403160000002</v>
+        <v>77.68597980000001</v>
       </c>
       <c r="N40">
-        <v>103.2948572888889</v>
+        <v>101.3029090888889</v>
       </c>
       <c r="O40">
-        <v>10.32948572888889</v>
+        <v>10.13029090888889</v>
       </c>
       <c r="P40">
-        <v>92.96537155999998</v>
+        <v>91.17261817999997</v>
       </c>
       <c r="Q40">
-        <v>121.86537156</v>
+        <v>120.07261818</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1059288747928678</v>
+        <v>0.1068510653677217</v>
       </c>
       <c r="T40">
-        <v>1.205202721161831</v>
+        <v>1.223686795478413</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.364636750156783</v>
+        <v>2.304005038614302</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09178494987431025</v>
+        <v>0.09197039737704252</v>
       </c>
       <c r="C41">
-        <v>1231.156767629304</v>
+        <v>1196.240343295887</v>
       </c>
       <c r="D41">
-        <v>2150.437767629304</v>
+        <v>2141.800343295887</v>
       </c>
       <c r="E41">
-        <v>139.881</v>
+        <v>166.16</v>
       </c>
       <c r="F41">
-        <v>1024.881</v>
+        <v>1051.16</v>
       </c>
       <c r="G41">
         <v>105.6</v>
@@ -4631,28 +4631,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M41">
-        <v>77.68597980000001</v>
+        <v>79.67792800000001</v>
       </c>
       <c r="N41">
-        <v>101.3029090888889</v>
+        <v>99.31096088888887</v>
       </c>
       <c r="O41">
-        <v>10.13029090888889</v>
+        <v>9.931096088888888</v>
       </c>
       <c r="P41">
-        <v>91.17261817999997</v>
+        <v>89.37986479999998</v>
       </c>
       <c r="Q41">
-        <v>120.07261818</v>
+        <v>118.2798648</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1068510653677217</v>
+        <v>0.1078039956284042</v>
       </c>
       <c r="T41">
-        <v>1.223686795478413</v>
+        <v>1.242787005605547</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.304005038614302</v>
+        <v>2.246404912648944</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09197039737704252</v>
+        <v>0.09215584487977477</v>
       </c>
       <c r="C42">
-        <v>1196.240343295887</v>
+        <v>1161.393027346832</v>
       </c>
       <c r="D42">
-        <v>2141.800343295887</v>
+        <v>2133.232027346832</v>
       </c>
       <c r="E42">
-        <v>166.16</v>
+        <v>192.439</v>
       </c>
       <c r="F42">
-        <v>1051.16</v>
+        <v>1077.439</v>
       </c>
       <c r="G42">
         <v>105.6</v>
@@ -4713,28 +4713,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M42">
-        <v>79.67792800000001</v>
+        <v>81.66987620000002</v>
       </c>
       <c r="N42">
-        <v>99.31096088888887</v>
+        <v>97.31901268888886</v>
       </c>
       <c r="O42">
-        <v>9.931096088888888</v>
+        <v>9.731901268888887</v>
       </c>
       <c r="P42">
-        <v>89.37986479999998</v>
+        <v>87.58711141999997</v>
       </c>
       <c r="Q42">
-        <v>118.2798648</v>
+        <v>116.48711142</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1078039956284042</v>
+        <v>0.1087892286097877</v>
       </c>
       <c r="T42">
-        <v>1.242787005605547</v>
+        <v>1.262534680482754</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.246404912648944</v>
+        <v>2.191614548925799</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09215584487977477</v>
+        <v>0.09234129238250702</v>
       </c>
       <c r="C43">
-        <v>1161.393027346832</v>
+        <v>1126.61399367848</v>
       </c>
       <c r="D43">
-        <v>2133.232027346832</v>
+        <v>2124.73199367848</v>
       </c>
       <c r="E43">
-        <v>192.439</v>
+        <v>218.718</v>
       </c>
       <c r="F43">
-        <v>1077.439</v>
+        <v>1103.718</v>
       </c>
       <c r="G43">
         <v>105.6</v>
@@ -4795,28 +4795,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M43">
-        <v>81.66987620000002</v>
+        <v>83.66182440000001</v>
       </c>
       <c r="N43">
-        <v>97.31901268888886</v>
+        <v>95.32706448888887</v>
       </c>
       <c r="O43">
-        <v>9.731901268888887</v>
+        <v>9.532706448888886</v>
       </c>
       <c r="P43">
-        <v>87.58711141999997</v>
+        <v>85.79435803999998</v>
       </c>
       <c r="Q43">
-        <v>116.48711142</v>
+        <v>114.69435804</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1087892286097877</v>
+        <v>0.1098084351422535</v>
       </c>
       <c r="T43">
-        <v>1.262534680482754</v>
+        <v>1.282963309666071</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.191614548925799</v>
+        <v>2.139433250141852</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09234129238250702</v>
+        <v>0.09252673988523925</v>
       </c>
       <c r="C44">
-        <v>1126.61399367848</v>
+        <v>1091.902429301622</v>
       </c>
       <c r="D44">
-        <v>2124.73199367848</v>
+        <v>2116.299429301622</v>
       </c>
       <c r="E44">
-        <v>218.718</v>
+        <v>244.997</v>
       </c>
       <c r="F44">
-        <v>1103.718</v>
+        <v>1129.997</v>
       </c>
       <c r="G44">
         <v>105.6</v>
@@ -4877,28 +4877,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M44">
-        <v>83.66182440000001</v>
+        <v>85.65377260000001</v>
       </c>
       <c r="N44">
-        <v>95.32706448888887</v>
+        <v>93.33511628888887</v>
       </c>
       <c r="O44">
-        <v>9.532706448888886</v>
+        <v>9.333511628888887</v>
       </c>
       <c r="P44">
-        <v>85.79435803999998</v>
+        <v>84.00160465999998</v>
       </c>
       <c r="Q44">
-        <v>114.69435804</v>
+        <v>112.90160466</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1098084351422535</v>
+        <v>0.1108634033074373</v>
       </c>
       <c r="T44">
-        <v>1.282963309666071</v>
+        <v>1.304108732855821</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.139433250141852</v>
+        <v>2.089678988510646</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09252673988523925</v>
+        <v>0.0927121873879715</v>
       </c>
       <c r="C45">
-        <v>1091.902429301622</v>
+        <v>1057.257534082285</v>
       </c>
       <c r="D45">
-        <v>2116.299429301622</v>
+        <v>2107.933534082285</v>
       </c>
       <c r="E45">
-        <v>244.997</v>
+        <v>271.276</v>
       </c>
       <c r="F45">
-        <v>1129.997</v>
+        <v>1156.276</v>
       </c>
       <c r="G45">
         <v>105.6</v>
@@ -4959,28 +4959,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M45">
-        <v>85.65377260000001</v>
+        <v>87.64572080000001</v>
       </c>
       <c r="N45">
-        <v>93.33511628888887</v>
+        <v>91.34316808888887</v>
       </c>
       <c r="O45">
-        <v>9.333511628888887</v>
+        <v>9.134316808888888</v>
       </c>
       <c r="P45">
-        <v>84.00160465999998</v>
+        <v>82.20885127999999</v>
       </c>
       <c r="Q45">
-        <v>112.90160466</v>
+        <v>111.10885128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1108634033074373</v>
+        <v>0.111956048907092</v>
       </c>
       <c r="T45">
-        <v>1.304108732855821</v>
+        <v>1.326009349730919</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.089678988510646</v>
+        <v>2.042186284226313</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0927121873879715</v>
+        <v>0.09864863489070376</v>
       </c>
       <c r="C46">
-        <v>1057.257534082285</v>
+        <v>794.1959418694905</v>
       </c>
       <c r="D46">
-        <v>2107.933534082285</v>
+        <v>1871.150941869491</v>
       </c>
       <c r="E46">
-        <v>271.276</v>
+        <v>297.5549999999999</v>
       </c>
       <c r="F46">
-        <v>1156.276</v>
+        <v>1182.555</v>
       </c>
       <c r="G46">
         <v>105.6</v>
@@ -5041,45 +5041,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M46">
-        <v>87.64572080000001</v>
+        <v>106.42995</v>
       </c>
       <c r="N46">
-        <v>91.34316808888887</v>
+        <v>72.55893888888887</v>
       </c>
       <c r="O46">
-        <v>9.134316808888888</v>
+        <v>7.255893888888888</v>
       </c>
       <c r="P46">
-        <v>82.20885127999999</v>
+        <v>65.30304499999998</v>
       </c>
       <c r="Q46">
-        <v>111.10885128</v>
+        <v>94.20304499999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.111956048907092</v>
+        <v>0.1130884270740068</v>
       </c>
       <c r="T46">
-        <v>1.326009349730919</v>
+        <v>1.348706352674202</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.1</v>
       </c>
       <c r="W46">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.042186284226313</v>
+        <v>1.681753011148543</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09864863489070376</v>
+        <v>0.09896188239343601</v>
       </c>
       <c r="C47">
-        <v>794.1959418694905</v>
+        <v>756.8914978222331</v>
       </c>
       <c r="D47">
-        <v>1871.150941869491</v>
+        <v>1860.125497822233</v>
       </c>
       <c r="E47">
-        <v>297.5549999999999</v>
+        <v>323.8339999999999</v>
       </c>
       <c r="F47">
-        <v>1182.555</v>
+        <v>1208.834</v>
       </c>
       <c r="G47">
         <v>105.6</v>
@@ -5123,28 +5123,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M47">
-        <v>106.42995</v>
+        <v>108.79506</v>
       </c>
       <c r="N47">
-        <v>72.55893888888887</v>
+        <v>70.19382888888887</v>
       </c>
       <c r="O47">
-        <v>7.255893888888888</v>
+        <v>7.019382888888888</v>
       </c>
       <c r="P47">
-        <v>65.30304499999998</v>
+        <v>63.17444599999999</v>
       </c>
       <c r="Q47">
-        <v>94.20304499999999</v>
+        <v>92.07444599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1130884270740068</v>
+        <v>0.1142627451730296</v>
       </c>
       <c r="T47">
-        <v>1.348706352674202</v>
+        <v>1.372243985356125</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.681753011148543</v>
+        <v>1.645193163080096</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09896188239343601</v>
+        <v>0.09927512989616827</v>
       </c>
       <c r="C48">
-        <v>756.8914978222331</v>
+        <v>719.7162238329454</v>
       </c>
       <c r="D48">
-        <v>1860.125497822233</v>
+        <v>1849.229223832946</v>
       </c>
       <c r="E48">
-        <v>323.8339999999999</v>
+        <v>350.1129999999999</v>
       </c>
       <c r="F48">
-        <v>1208.834</v>
+        <v>1235.113</v>
       </c>
       <c r="G48">
         <v>105.6</v>
@@ -5205,28 +5205,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M48">
-        <v>108.79506</v>
+        <v>111.16017</v>
       </c>
       <c r="N48">
-        <v>70.19382888888887</v>
+        <v>67.82871888888887</v>
       </c>
       <c r="O48">
-        <v>7.019382888888888</v>
+        <v>6.782871888888888</v>
       </c>
       <c r="P48">
-        <v>63.17444599999999</v>
+        <v>61.04584699999998</v>
       </c>
       <c r="Q48">
-        <v>92.07444599999999</v>
+        <v>89.94584699999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1142627451730296</v>
+        <v>0.1154813771625816</v>
       </c>
       <c r="T48">
-        <v>1.372243985356125</v>
+        <v>1.396669830592083</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.645193163080096</v>
+        <v>1.610189053227328</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09927512989616827</v>
+        <v>0.0995883773989005</v>
       </c>
       <c r="C49">
-        <v>719.7162238329454</v>
+        <v>682.667863157697</v>
       </c>
       <c r="D49">
-        <v>1849.229223832946</v>
+        <v>1838.459863157697</v>
       </c>
       <c r="E49">
-        <v>350.1129999999999</v>
+        <v>376.3919999999999</v>
       </c>
       <c r="F49">
-        <v>1235.113</v>
+        <v>1261.392</v>
       </c>
       <c r="G49">
         <v>105.6</v>
@@ -5287,28 +5287,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M49">
-        <v>111.16017</v>
+        <v>113.52528</v>
       </c>
       <c r="N49">
-        <v>67.82871888888887</v>
+        <v>65.46360888888888</v>
       </c>
       <c r="O49">
-        <v>6.782871888888888</v>
+        <v>6.546360888888889</v>
       </c>
       <c r="P49">
-        <v>61.04584699999998</v>
+        <v>58.91724799999999</v>
       </c>
       <c r="Q49">
-        <v>89.94584699999999</v>
+        <v>87.81724800000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1154813771625816</v>
+        <v>0.1167468796132702</v>
       </c>
       <c r="T49">
-        <v>1.396669830592083</v>
+        <v>1.42203513141404</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.610189053227328</v>
+        <v>1.576643447951759</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0995883773989005</v>
+        <v>0.09990162490163275</v>
       </c>
       <c r="C50">
-        <v>682.667863157697</v>
+        <v>645.7442113185941</v>
       </c>
       <c r="D50">
-        <v>1838.459863157697</v>
+        <v>1827.815211318594</v>
       </c>
       <c r="E50">
-        <v>376.3919999999999</v>
+        <v>402.6709999999999</v>
       </c>
       <c r="F50">
-        <v>1261.392</v>
+        <v>1287.671</v>
       </c>
       <c r="G50">
         <v>105.6</v>
@@ -5369,28 +5369,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M50">
-        <v>113.52528</v>
+        <v>115.89039</v>
       </c>
       <c r="N50">
-        <v>65.46360888888888</v>
+        <v>63.09849888888888</v>
       </c>
       <c r="O50">
-        <v>6.546360888888889</v>
+        <v>6.309849888888889</v>
       </c>
       <c r="P50">
-        <v>58.91724799999999</v>
+        <v>56.78864899999999</v>
       </c>
       <c r="Q50">
-        <v>87.81724800000001</v>
+        <v>85.688649</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1167468796132702</v>
+        <v>0.1180620096110446</v>
       </c>
       <c r="T50">
-        <v>1.42203513141404</v>
+        <v>1.448395149915289</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.576643447951759</v>
+        <v>1.544467051054784</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09990162490163275</v>
+        <v>0.100214872404365</v>
       </c>
       <c r="C51">
-        <v>645.7442113185941</v>
+        <v>608.9431145993958</v>
       </c>
       <c r="D51">
-        <v>1827.815211318594</v>
+        <v>1817.293114599396</v>
       </c>
       <c r="E51">
-        <v>402.6709999999999</v>
+        <v>428.9499999999999</v>
       </c>
       <c r="F51">
-        <v>1287.671</v>
+        <v>1313.95</v>
       </c>
       <c r="G51">
         <v>105.6</v>
@@ -5451,28 +5451,28 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M51">
-        <v>115.89039</v>
+        <v>118.2555</v>
       </c>
       <c r="N51">
-        <v>63.09849888888888</v>
+        <v>60.73338888888888</v>
       </c>
       <c r="O51">
-        <v>6.309849888888889</v>
+        <v>6.073338888888888</v>
       </c>
       <c r="P51">
-        <v>56.78864899999999</v>
+        <v>54.66004999999999</v>
       </c>
       <c r="Q51">
-        <v>85.688649</v>
+        <v>83.56004999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1180620096110446</v>
+        <v>0.11942974480873</v>
       </c>
       <c r="T51">
-        <v>1.448395149915289</v>
+        <v>1.475809569156587</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.544467051054784</v>
+        <v>1.513577710033689</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.100214872404365</v>
+        <v>0.127453392652119</v>
       </c>
       <c r="C52">
-        <v>608.9431145993958</v>
+        <v>-23.56146513877866</v>
       </c>
       <c r="D52">
-        <v>1817.293114599396</v>
+        <v>1211.067534861221</v>
       </c>
       <c r="E52">
-        <v>428.9499999999999</v>
+        <v>455.2289999999999</v>
       </c>
       <c r="F52">
-        <v>1313.95</v>
+        <v>1340.229</v>
       </c>
       <c r="G52">
         <v>105.6</v>
@@ -5533,45 +5533,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M52">
-        <v>118.2555</v>
+        <v>196.7456172</v>
       </c>
       <c r="N52">
-        <v>60.73338888888888</v>
+        <v>-17.75672831111115</v>
       </c>
       <c r="O52">
-        <v>6.073338888888888</v>
+        <v>-1.775672831111115</v>
       </c>
       <c r="P52">
-        <v>54.66004999999999</v>
+        <v>-15.98105548000003</v>
       </c>
       <c r="Q52">
-        <v>83.56004999999999</v>
+        <v>12.91894451999997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.11942974480873</v>
+        <v>0.1212173313209605</v>
       </c>
       <c r="T52">
-        <v>1.475809569156587</v>
+        <v>1.511639345387623</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1</v>
+        <v>0.09097477821167387</v>
       </c>
       <c r="W52">
-        <v>0.081</v>
+        <v>0.1334449025585263</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.513577710033689</v>
+        <v>0.9097477821167386</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.127453392652119</v>
+        <v>0.1284633926521191</v>
       </c>
       <c r="C53">
-        <v>-23.56146513877866</v>
+        <v>-64.63756178538642</v>
       </c>
       <c r="D53">
-        <v>1211.067534861221</v>
+        <v>1196.270438214614</v>
       </c>
       <c r="E53">
-        <v>455.2289999999999</v>
+        <v>481.5079999999999</v>
       </c>
       <c r="F53">
-        <v>1340.229</v>
+        <v>1366.508</v>
       </c>
       <c r="G53">
         <v>105.6</v>
@@ -5615,37 +5615,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M53">
-        <v>196.7456172</v>
+        <v>200.6033744</v>
       </c>
       <c r="N53">
-        <v>-17.75672831111115</v>
+        <v>-21.61448551111116</v>
       </c>
       <c r="O53">
-        <v>-1.775672831111115</v>
+        <v>-2.161448551111115</v>
       </c>
       <c r="P53">
-        <v>-15.98105548000003</v>
+        <v>-19.45303696000004</v>
       </c>
       <c r="Q53">
-        <v>12.91894451999997</v>
+        <v>9.446963039999964</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1212173313209605</v>
+        <v>0.1227885257234805</v>
       </c>
       <c r="T53">
-        <v>1.511639345387623</v>
+        <v>1.543131831749865</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.09097477821167387</v>
+        <v>0.08922526324606475</v>
       </c>
       <c r="W53">
-        <v>0.1334449025585263</v>
+        <v>0.1337017313554777</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9097477821167386</v>
+        <v>0.8922526324606475</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1284633926521191</v>
+        <v>0.129473392652119</v>
       </c>
       <c r="C54">
-        <v>-64.63756178538642</v>
+        <v>-105.3564345370517</v>
       </c>
       <c r="D54">
-        <v>1196.270438214614</v>
+        <v>1181.830565462948</v>
       </c>
       <c r="E54">
-        <v>481.5079999999999</v>
+        <v>507.7869999999999</v>
       </c>
       <c r="F54">
-        <v>1366.508</v>
+        <v>1392.787</v>
       </c>
       <c r="G54">
         <v>105.6</v>
@@ -5697,37 +5697,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M54">
-        <v>200.6033744</v>
+        <v>204.4611316</v>
       </c>
       <c r="N54">
-        <v>-21.61448551111116</v>
+        <v>-25.47224271111114</v>
       </c>
       <c r="O54">
-        <v>-2.161448551111115</v>
+        <v>-2.547224271111114</v>
       </c>
       <c r="P54">
-        <v>-19.45303696000004</v>
+        <v>-22.92501844000002</v>
       </c>
       <c r="Q54">
-        <v>9.446963039999964</v>
+        <v>5.974981559999982</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1227885257234805</v>
+        <v>0.124426579462278</v>
       </c>
       <c r="T54">
-        <v>1.543131831749865</v>
+        <v>1.575964423914756</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.08922526324606475</v>
+        <v>0.08754176771312014</v>
       </c>
       <c r="W54">
-        <v>0.1337017313554777</v>
+        <v>0.133948868499714</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8922526324606475</v>
+        <v>0.8754176771312013</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.129473392652119</v>
+        <v>0.1304833926521191</v>
       </c>
       <c r="C55">
-        <v>-105.3564345370517</v>
+        <v>-145.7308649837405</v>
       </c>
       <c r="D55">
-        <v>1181.830565462948</v>
+        <v>1167.73513501626</v>
       </c>
       <c r="E55">
-        <v>507.7869999999999</v>
+        <v>534.0659999999999</v>
       </c>
       <c r="F55">
-        <v>1392.787</v>
+        <v>1419.066</v>
       </c>
       <c r="G55">
         <v>105.6</v>
@@ -5779,37 +5779,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M55">
-        <v>204.4611316</v>
+        <v>208.3188888</v>
       </c>
       <c r="N55">
-        <v>-25.47224271111114</v>
+        <v>-29.32999991111114</v>
       </c>
       <c r="O55">
-        <v>-2.547224271111114</v>
+        <v>-2.932999991111115</v>
       </c>
       <c r="P55">
-        <v>-22.92501844000002</v>
+        <v>-26.39699992000003</v>
       </c>
       <c r="Q55">
-        <v>5.974981559999982</v>
+        <v>2.503000079999975</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.124426579462278</v>
+        <v>0.1261358529288492</v>
       </c>
       <c r="T55">
-        <v>1.575964423914756</v>
+        <v>1.610224520086816</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.08754176771312014</v>
+        <v>0.08592062386658088</v>
       </c>
       <c r="W55">
-        <v>0.133948868499714</v>
+        <v>0.1341868524163859</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8754176771312013</v>
+        <v>0.8592062386658087</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1304833926521191</v>
+        <v>0.1314933926521191</v>
       </c>
       <c r="C56">
-        <v>-145.7308649837405</v>
+        <v>-185.7730321295951</v>
       </c>
       <c r="D56">
-        <v>1167.73513501626</v>
+        <v>1153.971967870405</v>
       </c>
       <c r="E56">
-        <v>534.0659999999999</v>
+        <v>560.3450000000001</v>
       </c>
       <c r="F56">
-        <v>1419.066</v>
+        <v>1445.345</v>
       </c>
       <c r="G56">
         <v>105.6</v>
@@ -5861,37 +5861,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M56">
-        <v>208.3188888</v>
+        <v>212.1766460000001</v>
       </c>
       <c r="N56">
-        <v>-29.32999991111114</v>
+        <v>-33.18775711111118</v>
       </c>
       <c r="O56">
-        <v>-2.932999991111115</v>
+        <v>-3.318775711111118</v>
       </c>
       <c r="P56">
-        <v>-26.39699992000003</v>
+        <v>-29.86898140000006</v>
       </c>
       <c r="Q56">
-        <v>2.503000079999975</v>
+        <v>-0.9689814000000574</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1261358529288492</v>
+        <v>0.1279210941050459</v>
       </c>
       <c r="T56">
-        <v>1.610224520086816</v>
+        <v>1.646007287199857</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.08592062386658088</v>
+        <v>0.0843584307053703</v>
       </c>
       <c r="W56">
-        <v>0.1341868524163859</v>
+        <v>0.1344161823724516</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8592062386658087</v>
+        <v>0.8435843070537029</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1314933926521191</v>
+        <v>0.1325033926521191</v>
       </c>
       <c r="C57">
-        <v>-185.7730321295951</v>
+        <v>-225.4945474902745</v>
       </c>
       <c r="D57">
-        <v>1153.971967870405</v>
+        <v>1140.529452509726</v>
       </c>
       <c r="E57">
-        <v>560.3450000000001</v>
+        <v>586.6240000000001</v>
       </c>
       <c r="F57">
-        <v>1445.345</v>
+        <v>1471.624</v>
       </c>
       <c r="G57">
         <v>105.6</v>
@@ -5943,37 +5943,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M57">
-        <v>212.1766460000001</v>
+        <v>216.0344032000001</v>
       </c>
       <c r="N57">
-        <v>-33.18775711111118</v>
+        <v>-37.04551431111119</v>
       </c>
       <c r="O57">
-        <v>-3.318775711111118</v>
+        <v>-3.704551431111119</v>
       </c>
       <c r="P57">
-        <v>-29.86898140000006</v>
+        <v>-33.34096288000007</v>
       </c>
       <c r="Q57">
-        <v>-0.9689814000000574</v>
+        <v>-4.440962880000065</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1279210941050459</v>
+        <v>0.1297874826074333</v>
       </c>
       <c r="T57">
-        <v>1.646007287199857</v>
+        <v>1.683416543727126</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.0843584307053703</v>
+        <v>0.08285203015706011</v>
       </c>
       <c r="W57">
-        <v>0.1344161823724516</v>
+        <v>0.1346373219729436</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8435843070537029</v>
+        <v>0.8285203015706011</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1325033926521191</v>
+        <v>0.1335133926521191</v>
       </c>
       <c r="C58">
-        <v>-225.4945474902745</v>
+        <v>-264.9064877654671</v>
       </c>
       <c r="D58">
-        <v>1140.529452509726</v>
+        <v>1127.396512234533</v>
       </c>
       <c r="E58">
-        <v>586.6240000000001</v>
+        <v>612.9030000000001</v>
       </c>
       <c r="F58">
-        <v>1471.624</v>
+        <v>1497.903</v>
       </c>
       <c r="G58">
         <v>105.6</v>
@@ -6025,37 +6025,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M58">
-        <v>216.0344032000001</v>
+        <v>219.8921604000001</v>
       </c>
       <c r="N58">
-        <v>-37.04551431111119</v>
+        <v>-40.90327151111117</v>
       </c>
       <c r="O58">
-        <v>-3.704551431111119</v>
+        <v>-4.090327151111118</v>
       </c>
       <c r="P58">
-        <v>-33.34096288000007</v>
+        <v>-36.81294436000005</v>
       </c>
       <c r="Q58">
-        <v>-4.440962880000065</v>
+        <v>-7.912944360000047</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1297874826074333</v>
+        <v>0.1317406798773736</v>
       </c>
       <c r="T58">
-        <v>1.683416543727126</v>
+        <v>1.722565765674269</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.08285203015706011</v>
+        <v>0.08139848576833976</v>
       </c>
       <c r="W58">
-        <v>0.1346373219729436</v>
+        <v>0.1348507022892077</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8285203015706011</v>
+        <v>0.8139848576833976</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1335133926521191</v>
+        <v>0.1663269198717706</v>
       </c>
       <c r="C59">
-        <v>-264.9064877654671</v>
+        <v>-598.1198737176351</v>
       </c>
       <c r="D59">
-        <v>1127.396512234533</v>
+        <v>820.4621262823651</v>
       </c>
       <c r="E59">
-        <v>612.9030000000001</v>
+        <v>639.1820000000001</v>
       </c>
       <c r="F59">
-        <v>1497.903</v>
+        <v>1524.182</v>
       </c>
       <c r="G59">
         <v>105.6</v>
@@ -6107,45 +6107,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M59">
-        <v>219.8921604000001</v>
+        <v>306.0557456000001</v>
       </c>
       <c r="N59">
-        <v>-40.90327151111117</v>
+        <v>-127.0668567111112</v>
       </c>
       <c r="O59">
-        <v>-4.090327151111118</v>
+        <v>-12.70668567111112</v>
       </c>
       <c r="P59">
-        <v>-36.81294436000005</v>
+        <v>-114.3601710400001</v>
       </c>
       <c r="Q59">
-        <v>-7.912944360000047</v>
+        <v>-85.46017104000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1317406798773736</v>
+        <v>0.1349381418260052</v>
       </c>
       <c r="T59">
-        <v>1.722565765674269</v>
+        <v>1.786654605762779</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08139848576833976</v>
+        <v>0.05848244689476231</v>
       </c>
       <c r="W59">
-        <v>0.1348507022892077</v>
+        <v>0.1890567246635317</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8139848576833976</v>
+        <v>0.5848244689476231</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1663269198717706</v>
+        <v>0.1678769198717706</v>
       </c>
       <c r="C60">
-        <v>-598.1198737176345</v>
+        <v>-634.8162097470288</v>
       </c>
       <c r="D60">
-        <v>820.4621262823655</v>
+        <v>810.0447902529712</v>
       </c>
       <c r="E60">
-        <v>639.1819999999999</v>
+        <v>665.4609999999999</v>
       </c>
       <c r="F60">
-        <v>1524.182</v>
+        <v>1550.461</v>
       </c>
       <c r="G60">
         <v>105.6</v>
@@ -6189,37 +6189,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M60">
-        <v>306.0557456</v>
+        <v>311.3325688</v>
       </c>
       <c r="N60">
-        <v>-127.0668567111111</v>
+        <v>-132.3436799111111</v>
       </c>
       <c r="O60">
-        <v>-12.70668567111112</v>
+        <v>-13.23436799111111</v>
       </c>
       <c r="P60">
-        <v>-114.36017104</v>
+        <v>-119.10931192</v>
       </c>
       <c r="Q60">
-        <v>-85.46017104000002</v>
+        <v>-90.20931191999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1349381418260052</v>
+        <v>0.1371122428461516</v>
       </c>
       <c r="T60">
-        <v>1.786654605762779</v>
+        <v>1.830231547366749</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05848244689476232</v>
+        <v>0.05749121898129178</v>
       </c>
       <c r="W60">
-        <v>0.1890567246635317</v>
+        <v>0.1892557632285566</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5848244689476232</v>
+        <v>0.5749121898129178</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1678769198717706</v>
+        <v>0.1694269198717706</v>
       </c>
       <c r="C61">
-        <v>-634.8162097470288</v>
+        <v>-671.2513264422796</v>
       </c>
       <c r="D61">
-        <v>810.0447902529712</v>
+        <v>799.8886735577204</v>
       </c>
       <c r="E61">
-        <v>665.4609999999999</v>
+        <v>691.7399999999999</v>
       </c>
       <c r="F61">
-        <v>1550.461</v>
+        <v>1576.74</v>
       </c>
       <c r="G61">
         <v>105.6</v>
@@ -6271,37 +6271,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M61">
-        <v>311.3325688</v>
+        <v>316.609392</v>
       </c>
       <c r="N61">
-        <v>-132.3436799111111</v>
+        <v>-137.6205031111111</v>
       </c>
       <c r="O61">
-        <v>-13.23436799111111</v>
+        <v>-13.76205031111111</v>
       </c>
       <c r="P61">
-        <v>-119.10931192</v>
+        <v>-123.8584528</v>
       </c>
       <c r="Q61">
-        <v>-90.20931191999999</v>
+        <v>-94.95845280000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1371122428461516</v>
+        <v>0.1393950489173054</v>
       </c>
       <c r="T61">
-        <v>1.830231547366749</v>
+        <v>1.875987336050918</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05749121898129178</v>
+        <v>0.05653303199827025</v>
       </c>
       <c r="W61">
-        <v>0.1892557632285566</v>
+        <v>0.1894481671747474</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5749121898129178</v>
+        <v>0.5653303199827024</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1694269198717706</v>
+        <v>0.1709769198717706</v>
       </c>
       <c r="C62">
-        <v>-671.2513264422796</v>
+        <v>-707.4349274285039</v>
       </c>
       <c r="D62">
-        <v>799.8886735577204</v>
+        <v>789.9840725714961</v>
       </c>
       <c r="E62">
-        <v>691.7399999999999</v>
+        <v>718.0189999999999</v>
       </c>
       <c r="F62">
-        <v>1576.74</v>
+        <v>1603.019</v>
       </c>
       <c r="G62">
         <v>105.6</v>
@@ -6353,37 +6353,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M62">
-        <v>316.609392</v>
+        <v>321.8862152</v>
       </c>
       <c r="N62">
-        <v>-137.6205031111111</v>
+        <v>-142.8973263111112</v>
       </c>
       <c r="O62">
-        <v>-13.76205031111111</v>
+        <v>-14.28973263111112</v>
       </c>
       <c r="P62">
-        <v>-123.8584528</v>
+        <v>-128.60759368</v>
       </c>
       <c r="Q62">
-        <v>-94.95845280000002</v>
+        <v>-99.70759368000003</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1393950489173054</v>
+        <v>0.1417949219664671</v>
       </c>
       <c r="T62">
-        <v>1.875987336050918</v>
+        <v>1.924089575436839</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05653303199827025</v>
+        <v>0.05560626098190516</v>
       </c>
       <c r="W62">
-        <v>0.1894481671747474</v>
+        <v>0.1896342627948334</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5653303199827024</v>
+        <v>0.5560626098190515</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1709769198717706</v>
+        <v>0.1725269198717706</v>
       </c>
       <c r="C63">
-        <v>-707.4349274285039</v>
+        <v>-743.3762415897318</v>
       </c>
       <c r="D63">
-        <v>789.9840725714961</v>
+        <v>780.3217584102682</v>
       </c>
       <c r="E63">
-        <v>718.0189999999999</v>
+        <v>744.2979999999999</v>
       </c>
       <c r="F63">
-        <v>1603.019</v>
+        <v>1629.298</v>
       </c>
       <c r="G63">
         <v>105.6</v>
@@ -6435,37 +6435,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M63">
-        <v>321.8862152</v>
+        <v>327.1630384</v>
       </c>
       <c r="N63">
-        <v>-142.8973263111112</v>
+        <v>-148.1741495111111</v>
       </c>
       <c r="O63">
-        <v>-14.28973263111112</v>
+        <v>-14.81741495111111</v>
       </c>
       <c r="P63">
-        <v>-128.60759368</v>
+        <v>-133.35673456</v>
       </c>
       <c r="Q63">
-        <v>-99.70759368000003</v>
+        <v>-104.45673456</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1417949219664671</v>
+        <v>0.1443211041234794</v>
       </c>
       <c r="T63">
-        <v>1.924089575436839</v>
+        <v>1.974723511632545</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05560626098190516</v>
+        <v>0.05470938580477766</v>
       </c>
       <c r="W63">
-        <v>0.1896342627948334</v>
+        <v>0.1898143553304006</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5560626098190515</v>
+        <v>0.5470938580477767</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1725269198717706</v>
+        <v>0.1740769198717706</v>
       </c>
       <c r="C64">
-        <v>-743.3762415897318</v>
+        <v>-779.0840517509438</v>
       </c>
       <c r="D64">
-        <v>780.3217584102682</v>
+        <v>770.8929482490562</v>
       </c>
       <c r="E64">
-        <v>744.2979999999999</v>
+        <v>770.5769999999999</v>
       </c>
       <c r="F64">
-        <v>1629.298</v>
+        <v>1655.577</v>
       </c>
       <c r="G64">
         <v>105.6</v>
@@ -6517,37 +6517,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M64">
-        <v>327.1630384</v>
+        <v>332.4398616</v>
       </c>
       <c r="N64">
-        <v>-148.1741495111111</v>
+        <v>-153.4509727111111</v>
       </c>
       <c r="O64">
-        <v>-14.81741495111111</v>
+        <v>-15.34509727111111</v>
       </c>
       <c r="P64">
-        <v>-133.35673456</v>
+        <v>-138.10587544</v>
       </c>
       <c r="Q64">
-        <v>-104.45673456</v>
+        <v>-109.20587544</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1443211041234794</v>
+        <v>0.1469838366673572</v>
       </c>
       <c r="T64">
-        <v>1.974723511632545</v>
+        <v>2.028094417352344</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05470938580477766</v>
+        <v>0.05384098285549547</v>
       </c>
       <c r="W64">
-        <v>0.1898143553304006</v>
+        <v>0.1899887306426165</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5470938580477767</v>
+        <v>0.5384098285549547</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1740769198717706</v>
+        <v>0.1756269198717706</v>
       </c>
       <c r="C65">
-        <v>-779.0840517509438</v>
+        <v>-814.5667213055031</v>
       </c>
       <c r="D65">
-        <v>770.8929482490562</v>
+        <v>761.6892786944969</v>
       </c>
       <c r="E65">
-        <v>770.5769999999999</v>
+        <v>796.8559999999999</v>
       </c>
       <c r="F65">
-        <v>1655.577</v>
+        <v>1681.856</v>
       </c>
       <c r="G65">
         <v>105.6</v>
@@ -6599,37 +6599,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M65">
-        <v>332.4398616</v>
+        <v>337.7166848</v>
       </c>
       <c r="N65">
-        <v>-153.4509727111111</v>
+        <v>-158.7277959111111</v>
       </c>
       <c r="O65">
-        <v>-15.34509727111111</v>
+        <v>-15.87277959111111</v>
       </c>
       <c r="P65">
-        <v>-138.10587544</v>
+        <v>-142.85501632</v>
       </c>
       <c r="Q65">
-        <v>-109.20587544</v>
+        <v>-113.95501632</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1469838366673572</v>
+        <v>0.149794498797006</v>
       </c>
       <c r="T65">
-        <v>2.028094417352344</v>
+        <v>2.084430373389909</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05384098285549547</v>
+        <v>0.05299971749837837</v>
       </c>
       <c r="W65">
-        <v>0.1899887306426165</v>
+        <v>0.1901576567263256</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5384098285549547</v>
+        <v>0.5299971749837835</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1756269198717706</v>
+        <v>0.1771769198717706</v>
       </c>
       <c r="C66">
-        <v>-814.5667213055031</v>
+        <v>-849.8322189576694</v>
       </c>
       <c r="D66">
-        <v>761.6892786944969</v>
+        <v>752.7027810423308</v>
       </c>
       <c r="E66">
-        <v>796.8559999999999</v>
+        <v>823.1350000000001</v>
       </c>
       <c r="F66">
-        <v>1681.856</v>
+        <v>1708.135</v>
       </c>
       <c r="G66">
         <v>105.6</v>
@@ -6681,37 +6681,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M66">
-        <v>337.7166848</v>
+        <v>342.9935080000001</v>
       </c>
       <c r="N66">
-        <v>-158.7277959111111</v>
+        <v>-164.0046191111112</v>
       </c>
       <c r="O66">
-        <v>-15.87277959111111</v>
+        <v>-16.40046191111112</v>
       </c>
       <c r="P66">
-        <v>-142.85501632</v>
+        <v>-147.6041572000001</v>
       </c>
       <c r="Q66">
-        <v>-113.95501632</v>
+        <v>-118.7041572000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.149794498797006</v>
+        <v>0.1527657701912062</v>
       </c>
       <c r="T66">
-        <v>2.084430373389909</v>
+        <v>2.143985526915335</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05299971749837837</v>
+        <v>0.05218433722917253</v>
       </c>
       <c r="W66">
-        <v>0.1901576567263256</v>
+        <v>0.1903213850843822</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5299971749837835</v>
+        <v>0.5218433722917253</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1771769198717706</v>
+        <v>0.1787269198717706</v>
       </c>
       <c r="C67">
-        <v>-849.8322189576694</v>
+        <v>-884.8881417340423</v>
       </c>
       <c r="D67">
-        <v>752.7027810423308</v>
+        <v>743.9258582659579</v>
       </c>
       <c r="E67">
-        <v>823.1350000000001</v>
+        <v>849.4140000000001</v>
       </c>
       <c r="F67">
-        <v>1708.135</v>
+        <v>1734.414</v>
       </c>
       <c r="G67">
         <v>105.6</v>
@@ -6763,37 +6763,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M67">
-        <v>342.9935080000001</v>
+        <v>348.2703312</v>
       </c>
       <c r="N67">
-        <v>-164.0046191111112</v>
+        <v>-169.2814423111112</v>
       </c>
       <c r="O67">
-        <v>-16.40046191111112</v>
+        <v>-16.92814423111112</v>
       </c>
       <c r="P67">
-        <v>-147.6041572000001</v>
+        <v>-152.3532980800001</v>
       </c>
       <c r="Q67">
-        <v>-118.7041572000001</v>
+        <v>-123.4532980800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1527657701912062</v>
+        <v>0.1559118222556534</v>
       </c>
       <c r="T67">
-        <v>2.143985526915335</v>
+        <v>2.207043924765786</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05218433722917253</v>
+        <v>0.05139366545297295</v>
       </c>
       <c r="W67">
-        <v>0.1903213850843822</v>
+        <v>0.190480151977043</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5218433722917253</v>
+        <v>0.5139366545297295</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1787269198717706</v>
+        <v>0.1802769198717706</v>
       </c>
       <c r="C68">
-        <v>-884.8881417340423</v>
+        <v>-919.7417364036088</v>
       </c>
       <c r="D68">
-        <v>743.9258582659579</v>
+        <v>735.3512635963914</v>
       </c>
       <c r="E68">
-        <v>849.4140000000001</v>
+        <v>875.6930000000001</v>
       </c>
       <c r="F68">
-        <v>1734.414</v>
+        <v>1760.693</v>
       </c>
       <c r="G68">
         <v>105.6</v>
@@ -6845,37 +6845,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M68">
-        <v>348.2703312</v>
+        <v>353.5471544000001</v>
       </c>
       <c r="N68">
-        <v>-169.2814423111112</v>
+        <v>-174.5582655111112</v>
       </c>
       <c r="O68">
-        <v>-16.92814423111112</v>
+        <v>-17.45582655111112</v>
       </c>
       <c r="P68">
-        <v>-152.3532980800001</v>
+        <v>-157.1024389600001</v>
       </c>
       <c r="Q68">
-        <v>-123.4532980800001</v>
+        <v>-128.2024389600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1559118222556534</v>
+        <v>0.1592485441421884</v>
       </c>
       <c r="T68">
-        <v>2.207043924765786</v>
+        <v>2.273924043698083</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05139366545297295</v>
+        <v>0.05062659581934648</v>
       </c>
       <c r="W68">
-        <v>0.190480151977043</v>
+        <v>0.1906341795594752</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5139366545297295</v>
+        <v>0.5062659581934648</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1802769198717706</v>
+        <v>0.2058220289452611</v>
       </c>
       <c r="C69">
-        <v>-919.7417364036088</v>
+        <v>-1063.408500823997</v>
       </c>
       <c r="D69">
-        <v>735.3512635963914</v>
+        <v>617.9634991760028</v>
       </c>
       <c r="E69">
-        <v>875.6930000000001</v>
+        <v>901.9720000000001</v>
       </c>
       <c r="F69">
-        <v>1760.693</v>
+        <v>1786.972</v>
       </c>
       <c r="G69">
         <v>105.6</v>
@@ -6927,45 +6927,45 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M69">
-        <v>353.5471544000001</v>
+        <v>421.3679976000001</v>
       </c>
       <c r="N69">
-        <v>-174.5582655111112</v>
+        <v>-242.3791087111112</v>
       </c>
       <c r="O69">
-        <v>-17.45582655111112</v>
+        <v>-24.23791087111112</v>
       </c>
       <c r="P69">
-        <v>-157.1024389600001</v>
+        <v>-218.1411978400001</v>
       </c>
       <c r="Q69">
-        <v>-128.2024389600001</v>
+        <v>-189.2411978400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1592485441421884</v>
+        <v>0.1634035270012897</v>
       </c>
       <c r="T69">
-        <v>2.273924043698083</v>
+        <v>2.357205107337138</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05062659581934648</v>
+        <v>0.04247804529730828</v>
       </c>
       <c r="W69">
-        <v>0.1906341795594752</v>
+        <v>0.2257836769188947</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5062659581934648</v>
+        <v>0.4247804529730828</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2058220289452611</v>
+        <v>0.2077220289452611</v>
       </c>
       <c r="C70">
-        <v>-1063.408500823997</v>
+        <v>-1096.938710903827</v>
       </c>
       <c r="D70">
-        <v>617.9634991760028</v>
+        <v>610.7122890961729</v>
       </c>
       <c r="E70">
-        <v>901.9720000000001</v>
+        <v>928.2510000000001</v>
       </c>
       <c r="F70">
-        <v>1786.972</v>
+        <v>1813.251</v>
       </c>
       <c r="G70">
         <v>105.6</v>
@@ -7009,37 +7009,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M70">
-        <v>421.3679976000001</v>
+        <v>427.5645858000001</v>
       </c>
       <c r="N70">
-        <v>-242.3791087111112</v>
+        <v>-248.5756969111112</v>
       </c>
       <c r="O70">
-        <v>-24.23791087111112</v>
+        <v>-24.85756969111112</v>
       </c>
       <c r="P70">
-        <v>-218.1411978400001</v>
+        <v>-223.7181272200001</v>
       </c>
       <c r="Q70">
-        <v>-189.2411978400001</v>
+        <v>-194.8181272200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1634035270012897</v>
+        <v>0.1671971891626216</v>
       </c>
       <c r="T70">
-        <v>2.357205107337138</v>
+        <v>2.433243981767369</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04247804529730828</v>
+        <v>0.04186242145241975</v>
       </c>
       <c r="W70">
-        <v>0.2257836769188947</v>
+        <v>0.2259288410215194</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4247804529730828</v>
+        <v>0.4186242145241975</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2077220289452611</v>
+        <v>0.2096220289452611</v>
       </c>
       <c r="C71">
-        <v>-1096.938710903827</v>
+        <v>-1130.300722613263</v>
       </c>
       <c r="D71">
-        <v>610.7122890961729</v>
+        <v>603.6292773867375</v>
       </c>
       <c r="E71">
-        <v>928.2510000000001</v>
+        <v>954.5300000000001</v>
       </c>
       <c r="F71">
-        <v>1813.251</v>
+        <v>1839.53</v>
       </c>
       <c r="G71">
         <v>105.6</v>
@@ -7091,37 +7091,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M71">
-        <v>427.5645858000001</v>
+        <v>433.761174</v>
       </c>
       <c r="N71">
-        <v>-248.5756969111112</v>
+        <v>-254.7722851111112</v>
       </c>
       <c r="O71">
-        <v>-24.85756969111112</v>
+        <v>-25.47722851111112</v>
       </c>
       <c r="P71">
-        <v>-223.7181272200001</v>
+        <v>-229.2950566</v>
       </c>
       <c r="Q71">
-        <v>-194.8181272200001</v>
+        <v>-200.3950566</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1671971891626216</v>
+        <v>0.171243762134709</v>
       </c>
       <c r="T71">
-        <v>2.433243981767369</v>
+        <v>2.514352114492947</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04186242145241975</v>
+        <v>0.04126438686024234</v>
       </c>
       <c r="W71">
-        <v>0.2259288410215194</v>
+        <v>0.2260698575783548</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4186242145241975</v>
+        <v>0.4126438686024233</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2096220289452611</v>
+        <v>0.2115220289452611</v>
       </c>
       <c r="C72">
-        <v>-1130.300722613263</v>
+        <v>-1163.50032112593</v>
       </c>
       <c r="D72">
-        <v>603.6292773867375</v>
+        <v>596.70867887407</v>
       </c>
       <c r="E72">
-        <v>954.5300000000001</v>
+        <v>980.8090000000001</v>
       </c>
       <c r="F72">
-        <v>1839.53</v>
+        <v>1865.809</v>
       </c>
       <c r="G72">
         <v>105.6</v>
@@ -7173,37 +7173,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M72">
-        <v>433.761174</v>
+        <v>439.9577622</v>
       </c>
       <c r="N72">
-        <v>-254.7722851111112</v>
+        <v>-260.9688733111112</v>
       </c>
       <c r="O72">
-        <v>-25.47722851111112</v>
+        <v>-26.09688733111112</v>
       </c>
       <c r="P72">
-        <v>-229.2950566</v>
+        <v>-234.87198598</v>
       </c>
       <c r="Q72">
-        <v>-200.3950566</v>
+        <v>-205.97198598</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.171243762134709</v>
+        <v>0.1755694091048714</v>
       </c>
       <c r="T72">
-        <v>2.514352114492947</v>
+        <v>2.601053911544429</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04126438686024234</v>
+        <v>0.04068319831291498</v>
       </c>
       <c r="W72">
-        <v>0.2260698575783548</v>
+        <v>0.2262069018378146</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4126438686024233</v>
+        <v>0.4068319831291497</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2115220289452611</v>
+        <v>0.2134220289452611</v>
       </c>
       <c r="C73">
-        <v>-1163.50032112593</v>
+        <v>-1196.54302931509</v>
       </c>
       <c r="D73">
-        <v>596.7086788740702</v>
+        <v>589.9449706849098</v>
       </c>
       <c r="E73">
-        <v>980.8089999999999</v>
+        <v>1007.088</v>
       </c>
       <c r="F73">
-        <v>1865.809</v>
+        <v>1892.088</v>
       </c>
       <c r="G73">
         <v>105.6</v>
@@ -7255,37 +7255,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M73">
-        <v>439.9577622</v>
+        <v>446.1543504</v>
       </c>
       <c r="N73">
-        <v>-260.9688733111111</v>
+        <v>-267.1654615111111</v>
       </c>
       <c r="O73">
-        <v>-26.09688733111111</v>
+        <v>-26.71654615111111</v>
       </c>
       <c r="P73">
-        <v>-234.87198598</v>
+        <v>-240.44891536</v>
       </c>
       <c r="Q73">
-        <v>-205.97198598</v>
+        <v>-211.54891536</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1755694091048714</v>
+        <v>0.1802040308586168</v>
       </c>
       <c r="T73">
-        <v>2.601053911544428</v>
+        <v>2.693948694099586</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04068319831291498</v>
+        <v>0.04011815389190227</v>
       </c>
       <c r="W73">
-        <v>0.2262069018378146</v>
+        <v>0.2263401393122894</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4068319831291498</v>
+        <v>0.4011815389190226</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2134220289452611</v>
+        <v>0.2153220289452611</v>
       </c>
       <c r="C74">
-        <v>-1196.54302931509</v>
+        <v>-1229.434122452928</v>
       </c>
       <c r="D74">
-        <v>589.9449706849098</v>
+        <v>583.3328775470717</v>
       </c>
       <c r="E74">
-        <v>1007.088</v>
+        <v>1033.367</v>
       </c>
       <c r="F74">
-        <v>1892.088</v>
+        <v>1918.367</v>
       </c>
       <c r="G74">
         <v>105.6</v>
@@ -7337,37 +7337,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M74">
-        <v>446.1543504</v>
+        <v>452.3509386</v>
       </c>
       <c r="N74">
-        <v>-267.1654615111111</v>
+        <v>-273.3620497111111</v>
       </c>
       <c r="O74">
-        <v>-26.71654615111111</v>
+        <v>-27.33620497111112</v>
       </c>
       <c r="P74">
-        <v>-240.44891536</v>
+        <v>-246.02584474</v>
       </c>
       <c r="Q74">
-        <v>-211.54891536</v>
+        <v>-217.12584474</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1802040308586168</v>
+        <v>0.1851819579274544</v>
       </c>
       <c r="T74">
-        <v>2.693948694099586</v>
+        <v>2.79372457165883</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04011815389190227</v>
+        <v>0.0395685901399584</v>
       </c>
       <c r="W74">
-        <v>0.2263401393122894</v>
+        <v>0.2264697264449978</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4011815389190226</v>
+        <v>0.395685901399584</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2153220289452611</v>
+        <v>0.2172220289452611</v>
       </c>
       <c r="C75">
-        <v>-1229.434122452928</v>
+        <v>-1262.178641932303</v>
       </c>
       <c r="D75">
-        <v>583.3328775470717</v>
+        <v>576.8673580676975</v>
       </c>
       <c r="E75">
-        <v>1033.367</v>
+        <v>1059.646</v>
       </c>
       <c r="F75">
-        <v>1918.367</v>
+        <v>1944.646</v>
       </c>
       <c r="G75">
         <v>105.6</v>
@@ -7419,37 +7419,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M75">
-        <v>452.3509386</v>
+        <v>458.5475268</v>
       </c>
       <c r="N75">
-        <v>-273.3620497111111</v>
+        <v>-279.5586379111111</v>
       </c>
       <c r="O75">
-        <v>-27.33620497111112</v>
+        <v>-27.95586379111111</v>
       </c>
       <c r="P75">
-        <v>-246.02584474</v>
+        <v>-251.60277412</v>
       </c>
       <c r="Q75">
-        <v>-217.12584474</v>
+        <v>-222.70277412</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1851819579274544</v>
+        <v>0.1905428024631257</v>
       </c>
       <c r="T75">
-        <v>2.79372457165883</v>
+        <v>2.901175516722631</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0395685901399584</v>
+        <v>0.0390338794623914</v>
       </c>
       <c r="W75">
-        <v>0.2264697264449978</v>
+        <v>0.2265958112227681</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.395685901399584</v>
+        <v>0.390338794623914</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2172220289452611</v>
+        <v>0.2191220289452611</v>
       </c>
       <c r="C76">
-        <v>-1262.178641932303</v>
+        <v>-1294.781408085968</v>
       </c>
       <c r="D76">
-        <v>576.8673580676975</v>
+        <v>570.5435919140323</v>
       </c>
       <c r="E76">
-        <v>1059.646</v>
+        <v>1085.925</v>
       </c>
       <c r="F76">
-        <v>1944.646</v>
+        <v>1970.925</v>
       </c>
       <c r="G76">
         <v>105.6</v>
@@ -7501,37 +7501,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M76">
-        <v>458.5475268</v>
+        <v>464.7441150000001</v>
       </c>
       <c r="N76">
-        <v>-279.5586379111111</v>
+        <v>-285.7552261111112</v>
       </c>
       <c r="O76">
-        <v>-27.95586379111111</v>
+        <v>-28.57552261111112</v>
       </c>
       <c r="P76">
-        <v>-251.60277412</v>
+        <v>-257.1797035000001</v>
       </c>
       <c r="Q76">
-        <v>-222.70277412</v>
+        <v>-228.2797035000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1905428024631257</v>
+        <v>0.1963325145616508</v>
       </c>
       <c r="T76">
-        <v>2.901175516722631</v>
+        <v>3.017222537391536</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0390338794623914</v>
+        <v>0.03851342773622617</v>
       </c>
       <c r="W76">
-        <v>0.2265958112227681</v>
+        <v>0.2267185337397979</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.390338794623914</v>
+        <v>0.3851342773622617</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2191220289452611</v>
+        <v>0.2210220289452611</v>
       </c>
       <c r="C77">
-        <v>-1294.781408085968</v>
+        <v>-1327.247032171774</v>
       </c>
       <c r="D77">
-        <v>570.5435919140323</v>
+        <v>564.3569678282257</v>
       </c>
       <c r="E77">
-        <v>1085.925</v>
+        <v>1112.204</v>
       </c>
       <c r="F77">
-        <v>1970.925</v>
+        <v>1997.204</v>
       </c>
       <c r="G77">
         <v>105.6</v>
@@ -7583,37 +7583,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M77">
-        <v>464.7441150000001</v>
+        <v>470.9407032000001</v>
       </c>
       <c r="N77">
-        <v>-285.7552261111112</v>
+        <v>-291.9518143111112</v>
       </c>
       <c r="O77">
-        <v>-28.57552261111112</v>
+        <v>-29.19518143111112</v>
       </c>
       <c r="P77">
-        <v>-257.1797035000001</v>
+        <v>-262.7566328800001</v>
       </c>
       <c r="Q77">
-        <v>-228.2797035000001</v>
+        <v>-233.8566328800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1963325145616508</v>
+        <v>0.2026047026683862</v>
       </c>
       <c r="T77">
-        <v>3.017222537391536</v>
+        <v>3.142940143116184</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03851342773622617</v>
+        <v>0.03800667210811793</v>
       </c>
       <c r="W77">
-        <v>0.2267185337397979</v>
+        <v>0.2268380267169058</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3851342773622617</v>
+        <v>0.3800667210811793</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2210220289452611</v>
+        <v>0.2229220289452611</v>
       </c>
       <c r="C78">
-        <v>-1327.247032171774</v>
+        <v>-1359.579927586472</v>
       </c>
       <c r="D78">
-        <v>564.3569678282257</v>
+        <v>558.3030724135284</v>
       </c>
       <c r="E78">
-        <v>1112.204</v>
+        <v>1138.483</v>
       </c>
       <c r="F78">
-        <v>1997.204</v>
+        <v>2023.483</v>
       </c>
       <c r="G78">
         <v>105.6</v>
@@ -7665,37 +7665,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M78">
-        <v>470.9407032000001</v>
+        <v>477.1372914</v>
       </c>
       <c r="N78">
-        <v>-291.9518143111112</v>
+        <v>-298.1484025111112</v>
       </c>
       <c r="O78">
-        <v>-29.19518143111112</v>
+        <v>-29.81484025111112</v>
       </c>
       <c r="P78">
-        <v>-262.7566328800001</v>
+        <v>-268.3335622600001</v>
       </c>
       <c r="Q78">
-        <v>-233.8566328800001</v>
+        <v>-239.4335622600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2026047026683862</v>
+        <v>0.2094222984365769</v>
       </c>
       <c r="T78">
-        <v>3.142940143116184</v>
+        <v>3.279589714556018</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03800667210811793</v>
+        <v>0.03751307896385667</v>
       </c>
       <c r="W78">
-        <v>0.2268380267169058</v>
+        <v>0.2269544159803226</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3800667210811793</v>
+        <v>0.3751307896385666</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2229220289452611</v>
+        <v>0.2248220289452612</v>
       </c>
       <c r="C79">
-        <v>-1359.579927586472</v>
+        <v>-1391.784320365425</v>
       </c>
       <c r="D79">
-        <v>558.3030724135284</v>
+        <v>552.3776796345755</v>
       </c>
       <c r="E79">
-        <v>1138.483</v>
+        <v>1164.762</v>
       </c>
       <c r="F79">
-        <v>2023.483</v>
+        <v>2049.762</v>
       </c>
       <c r="G79">
         <v>105.6</v>
@@ -7747,37 +7747,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M79">
-        <v>477.1372914</v>
+        <v>483.3338796</v>
       </c>
       <c r="N79">
-        <v>-298.1484025111112</v>
+        <v>-304.3449907111112</v>
       </c>
       <c r="O79">
-        <v>-29.81484025111112</v>
+        <v>-30.43449907111112</v>
       </c>
       <c r="P79">
-        <v>-268.3335622600001</v>
+        <v>-273.91049164</v>
       </c>
       <c r="Q79">
-        <v>-239.4335622600001</v>
+        <v>-245.01049164</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2094222984365769</v>
+        <v>0.2168596756382396</v>
       </c>
       <c r="T79">
-        <v>3.279589714556018</v>
+        <v>3.428661974308565</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03751307896385667</v>
+        <v>0.03703214205406363</v>
       </c>
       <c r="W79">
-        <v>0.2269544159803226</v>
+        <v>0.2270678209036518</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3751307896385666</v>
+        <v>0.3703214205406363</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2248220289452612</v>
+        <v>0.2267220289452611</v>
       </c>
       <c r="C80">
-        <v>-1391.784320365425</v>
+        <v>-1423.864259020735</v>
       </c>
       <c r="D80">
-        <v>552.3776796345755</v>
+        <v>546.5767409792655</v>
       </c>
       <c r="E80">
-        <v>1164.762</v>
+        <v>1191.041</v>
       </c>
       <c r="F80">
-        <v>2049.762</v>
+        <v>2076.041</v>
       </c>
       <c r="G80">
         <v>105.6</v>
@@ -7829,37 +7829,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M80">
-        <v>483.3338796</v>
+        <v>489.5304678000001</v>
       </c>
       <c r="N80">
-        <v>-304.3449907111112</v>
+        <v>-310.5415789111112</v>
       </c>
       <c r="O80">
-        <v>-30.43449907111112</v>
+        <v>-31.05415789111112</v>
       </c>
       <c r="P80">
-        <v>-273.91049164</v>
+        <v>-279.4874210200001</v>
       </c>
       <c r="Q80">
-        <v>-245.01049164</v>
+        <v>-250.5874210200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2168596756382396</v>
+        <v>0.2250053744781557</v>
       </c>
       <c r="T80">
-        <v>3.428661974308565</v>
+        <v>3.591931592132782</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03703214205406363</v>
+        <v>0.03656338076224004</v>
       </c>
       <c r="W80">
-        <v>0.2270678209036518</v>
+        <v>0.2271783548162638</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3703214205406363</v>
+        <v>0.3656338076224004</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2267220289452611</v>
+        <v>0.2286220289452611</v>
       </c>
       <c r="C81">
-        <v>-1423.864259020735</v>
+        <v>-1455.823623765902</v>
       </c>
       <c r="D81">
-        <v>546.5767409792655</v>
+        <v>540.8963762340982</v>
       </c>
       <c r="E81">
-        <v>1191.041</v>
+        <v>1217.32</v>
       </c>
       <c r="F81">
-        <v>2076.041</v>
+        <v>2102.32</v>
       </c>
       <c r="G81">
         <v>105.6</v>
@@ -7911,37 +7911,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M81">
-        <v>489.5304678000001</v>
+        <v>495.7270560000001</v>
       </c>
       <c r="N81">
-        <v>-310.5415789111112</v>
+        <v>-316.7381671111112</v>
       </c>
       <c r="O81">
-        <v>-31.05415789111112</v>
+        <v>-31.67381671111112</v>
       </c>
       <c r="P81">
-        <v>-279.4874210200001</v>
+        <v>-285.0643504000001</v>
       </c>
       <c r="Q81">
-        <v>-250.5874210200001</v>
+        <v>-256.1643504000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2250053744781557</v>
+        <v>0.2339656432020635</v>
       </c>
       <c r="T81">
-        <v>3.591931592132782</v>
+        <v>3.771528171739421</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03656338076224004</v>
+        <v>0.03610633850271204</v>
       </c>
       <c r="W81">
-        <v>0.2271783548162638</v>
+        <v>0.2272861253810605</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3656338076224004</v>
+        <v>0.3610633850271203</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2286220289452611</v>
+        <v>0.2305220289452611</v>
       </c>
       <c r="C82">
-        <v>-1455.823623765902</v>
+        <v>-1487.666135171189</v>
       </c>
       <c r="D82">
-        <v>540.8963762340982</v>
+        <v>535.3328648288108</v>
       </c>
       <c r="E82">
-        <v>1217.32</v>
+        <v>1243.599</v>
       </c>
       <c r="F82">
-        <v>2102.32</v>
+        <v>2128.599</v>
       </c>
       <c r="G82">
         <v>105.6</v>
@@ -7993,37 +7993,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M82">
-        <v>495.7270560000001</v>
+        <v>501.9236442000001</v>
       </c>
       <c r="N82">
-        <v>-316.7381671111112</v>
+        <v>-322.9347553111112</v>
       </c>
       <c r="O82">
-        <v>-31.67381671111112</v>
+        <v>-32.29347553111112</v>
       </c>
       <c r="P82">
-        <v>-285.0643504000001</v>
+        <v>-290.64127978</v>
       </c>
       <c r="Q82">
-        <v>-256.1643504000001</v>
+        <v>-261.74127978</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2339656432020635</v>
+        <v>0.2438690981074353</v>
       </c>
       <c r="T82">
-        <v>3.771528171739421</v>
+        <v>3.970029654462548</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03610633850271204</v>
+        <v>0.03566058123724646</v>
       </c>
       <c r="W82">
-        <v>0.2272861253810605</v>
+        <v>0.2273912349442573</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3610633850271203</v>
+        <v>0.3566058123724646</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2305220289452611</v>
+        <v>0.2324220289452611</v>
       </c>
       <c r="C83">
-        <v>-1487.666135171189</v>
+        <v>-1519.395362290267</v>
       </c>
       <c r="D83">
-        <v>535.3328648288108</v>
+        <v>529.8826377097334</v>
       </c>
       <c r="E83">
-        <v>1243.599</v>
+        <v>1269.878</v>
       </c>
       <c r="F83">
-        <v>2128.599</v>
+        <v>2154.878</v>
       </c>
       <c r="G83">
         <v>105.6</v>
@@ -8075,37 +8075,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M83">
-        <v>501.9236442000001</v>
+        <v>508.1202324000001</v>
       </c>
       <c r="N83">
-        <v>-322.9347553111112</v>
+        <v>-329.1313435111112</v>
       </c>
       <c r="O83">
-        <v>-32.29347553111112</v>
+        <v>-32.91313435111112</v>
       </c>
       <c r="P83">
-        <v>-290.64127978</v>
+        <v>-296.2182091600001</v>
       </c>
       <c r="Q83">
-        <v>-261.74127978</v>
+        <v>-267.31820916</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2438690981074353</v>
+        <v>0.2548729368911817</v>
       </c>
       <c r="T83">
-        <v>3.970029654462548</v>
+        <v>4.190586857488246</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03566058123724646</v>
+        <v>0.03522569610020686</v>
       </c>
       <c r="W83">
-        <v>0.2273912349442573</v>
+        <v>0.2274937808595712</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3566058123724646</v>
+        <v>0.3522569610020686</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2324220289452611</v>
+        <v>0.2343220289452611</v>
       </c>
       <c r="C84">
-        <v>-1519.395362290267</v>
+        <v>-1551.014730295434</v>
       </c>
       <c r="D84">
-        <v>529.8826377097334</v>
+        <v>524.542269704566</v>
       </c>
       <c r="E84">
-        <v>1269.878</v>
+        <v>1296.157</v>
       </c>
       <c r="F84">
-        <v>2154.878</v>
+        <v>2181.157</v>
       </c>
       <c r="G84">
         <v>105.6</v>
@@ -8157,37 +8157,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M84">
-        <v>508.1202324000001</v>
+        <v>514.3168206</v>
       </c>
       <c r="N84">
-        <v>-329.1313435111112</v>
+        <v>-335.3279317111111</v>
       </c>
       <c r="O84">
-        <v>-32.91313435111112</v>
+        <v>-33.53279317111112</v>
       </c>
       <c r="P84">
-        <v>-296.2182091600001</v>
+        <v>-301.79513854</v>
       </c>
       <c r="Q84">
-        <v>-267.31820916</v>
+        <v>-272.8951385400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2548729368911817</v>
+        <v>0.2671713449436042</v>
       </c>
       <c r="T84">
-        <v>4.190586857488246</v>
+        <v>4.437091966752261</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03522569610020686</v>
+        <v>0.03480129012309594</v>
       </c>
       <c r="W84">
-        <v>0.2274937808595712</v>
+        <v>0.227593855788974</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3522569610020686</v>
+        <v>0.3480129012309594</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2343220289452611</v>
+        <v>0.2362220289452611</v>
       </c>
       <c r="C85">
-        <v>-1551.014730295434</v>
+        <v>-1582.527527655745</v>
       </c>
       <c r="D85">
-        <v>524.542269704566</v>
+        <v>519.3084723442556</v>
       </c>
       <c r="E85">
-        <v>1296.157</v>
+        <v>1322.436</v>
       </c>
       <c r="F85">
-        <v>2181.157</v>
+        <v>2207.436</v>
       </c>
       <c r="G85">
         <v>105.6</v>
@@ -8239,37 +8239,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M85">
-        <v>514.3168206</v>
+        <v>520.5134088000001</v>
       </c>
       <c r="N85">
-        <v>-335.3279317111111</v>
+        <v>-341.5245199111112</v>
       </c>
       <c r="O85">
-        <v>-33.53279317111112</v>
+        <v>-34.15245199111112</v>
       </c>
       <c r="P85">
-        <v>-301.79513854</v>
+        <v>-307.3720679200001</v>
       </c>
       <c r="Q85">
-        <v>-272.8951385400001</v>
+        <v>-278.4720679200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2671713449436042</v>
+        <v>0.2810070540025795</v>
       </c>
       <c r="T85">
-        <v>4.437091966752261</v>
+        <v>4.714410214674278</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03480129012309594</v>
+        <v>0.03438698905020194</v>
       </c>
       <c r="W85">
-        <v>0.227593855788974</v>
+        <v>0.2276915479819624</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3480129012309594</v>
+        <v>0.3438698905020193</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2362220289452611</v>
+        <v>0.2381220289452611</v>
       </c>
       <c r="C86">
-        <v>-1582.527527655745</v>
+        <v>-1613.936912889642</v>
       </c>
       <c r="D86">
-        <v>519.3084723442556</v>
+        <v>514.1780871103576</v>
       </c>
       <c r="E86">
-        <v>1322.436</v>
+        <v>1348.715</v>
       </c>
       <c r="F86">
-        <v>2207.436</v>
+        <v>2233.715</v>
       </c>
       <c r="G86">
         <v>105.6</v>
@@ -8321,37 +8321,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M86">
-        <v>520.5134088000001</v>
+        <v>526.709997</v>
       </c>
       <c r="N86">
-        <v>-341.5245199111112</v>
+        <v>-347.7211081111112</v>
       </c>
       <c r="O86">
-        <v>-34.15245199111112</v>
+        <v>-34.77211081111112</v>
       </c>
       <c r="P86">
-        <v>-307.3720679200001</v>
+        <v>-312.9489973</v>
       </c>
       <c r="Q86">
-        <v>-278.4720679200001</v>
+        <v>-284.0489973</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2810070540025793</v>
+        <v>0.296687524269418</v>
       </c>
       <c r="T86">
-        <v>4.714410214674275</v>
+        <v>5.028704228985894</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03438698905020194</v>
+        <v>0.03398243623784663</v>
       </c>
       <c r="W86">
-        <v>0.2276915479819624</v>
+        <v>0.2277869415351158</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3438698905020193</v>
+        <v>0.3398243623784662</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2381220289452611</v>
+        <v>0.2400220289452611</v>
       </c>
       <c r="C87">
-        <v>-1613.936912889642</v>
+        <v>-1645.24592092125</v>
       </c>
       <c r="D87">
-        <v>514.1780871103576</v>
+        <v>509.1480790787504</v>
       </c>
       <c r="E87">
-        <v>1348.715</v>
+        <v>1374.994</v>
       </c>
       <c r="F87">
-        <v>2233.715</v>
+        <v>2259.994</v>
       </c>
       <c r="G87">
         <v>105.6</v>
@@ -8403,37 +8403,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M87">
-        <v>526.709997</v>
+        <v>532.9065852000001</v>
       </c>
       <c r="N87">
-        <v>-347.7211081111112</v>
+        <v>-353.9176963111112</v>
       </c>
       <c r="O87">
-        <v>-34.77211081111112</v>
+        <v>-35.39176963111112</v>
       </c>
       <c r="P87">
-        <v>-312.9489973</v>
+        <v>-318.5259266800001</v>
       </c>
       <c r="Q87">
-        <v>-284.0489973</v>
+        <v>-289.6259266800001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.296687524269418</v>
+        <v>0.3146080617172335</v>
       </c>
       <c r="T87">
-        <v>5.028704228985894</v>
+        <v>5.387897388199172</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03398243623784663</v>
+        <v>0.0335872916304298</v>
       </c>
       <c r="W87">
-        <v>0.2277869415351158</v>
+        <v>0.2278801166335447</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3398243623784662</v>
+        <v>0.3358729163042979</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2400220289452611</v>
+        <v>0.2419220289452611</v>
       </c>
       <c r="C88">
-        <v>-1645.24592092125</v>
+        <v>-1676.457469067178</v>
       </c>
       <c r="D88">
-        <v>509.1480790787504</v>
+        <v>504.2155309328222</v>
       </c>
       <c r="E88">
-        <v>1374.994</v>
+        <v>1401.273</v>
       </c>
       <c r="F88">
-        <v>2259.994</v>
+        <v>2286.273</v>
       </c>
       <c r="G88">
         <v>105.6</v>
@@ -8485,37 +8485,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M88">
-        <v>532.9065852000001</v>
+        <v>539.1031734000001</v>
       </c>
       <c r="N88">
-        <v>-353.9176963111112</v>
+        <v>-360.1142845111112</v>
       </c>
       <c r="O88">
-        <v>-35.39176963111112</v>
+        <v>-36.01142845111112</v>
       </c>
       <c r="P88">
-        <v>-318.5259266800001</v>
+        <v>-324.1028560600001</v>
       </c>
       <c r="Q88">
-        <v>-289.6259266800001</v>
+        <v>-295.20285606</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3146080617172335</v>
+        <v>0.3352856049262515</v>
       </c>
       <c r="T88">
-        <v>5.387897388199172</v>
+        <v>5.802351033445262</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0335872916304298</v>
+        <v>0.03320123080709153</v>
       </c>
       <c r="W88">
-        <v>0.2278801166335447</v>
+        <v>0.2279711497756878</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3358729163042979</v>
+        <v>0.3320123080709153</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2419220289452611</v>
+        <v>0.2438220289452611</v>
       </c>
       <c r="C89">
-        <v>-1676.457469067178</v>
+        <v>-1707.574362678687</v>
       </c>
       <c r="D89">
-        <v>504.2155309328222</v>
+        <v>499.377637321313</v>
       </c>
       <c r="E89">
-        <v>1401.273</v>
+        <v>1427.552</v>
       </c>
       <c r="F89">
-        <v>2286.273</v>
+        <v>2312.552</v>
       </c>
       <c r="G89">
         <v>105.6</v>
@@ -8567,37 +8567,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M89">
-        <v>539.1031734000001</v>
+        <v>545.2997616</v>
       </c>
       <c r="N89">
-        <v>-360.1142845111112</v>
+        <v>-366.3108727111111</v>
       </c>
       <c r="O89">
-        <v>-36.01142845111112</v>
+        <v>-36.63108727111111</v>
       </c>
       <c r="P89">
-        <v>-324.1028560600001</v>
+        <v>-329.67978544</v>
       </c>
       <c r="Q89">
-        <v>-295.20285606</v>
+        <v>-300.7797854400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3352856049262515</v>
+        <v>0.3594094053367725</v>
       </c>
       <c r="T89">
-        <v>5.802351033445262</v>
+        <v>6.285880286232367</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03320123080709153</v>
+        <v>0.03282394409337458</v>
       </c>
       <c r="W89">
-        <v>0.2279711497756878</v>
+        <v>0.2280601139827823</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3320123080709153</v>
+        <v>0.3282394409337458</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2438220289452611</v>
+        <v>0.2457220289452611</v>
       </c>
       <c r="C90">
-        <v>-1707.574362678687</v>
+        <v>-1738.599300462113</v>
       </c>
       <c r="D90">
-        <v>499.377637321313</v>
+        <v>494.6316995378871</v>
       </c>
       <c r="E90">
-        <v>1427.552</v>
+        <v>1453.831</v>
       </c>
       <c r="F90">
-        <v>2312.552</v>
+        <v>2338.831</v>
       </c>
       <c r="G90">
         <v>105.6</v>
@@ -8649,37 +8649,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M90">
-        <v>545.2997616</v>
+        <v>551.4963498000001</v>
       </c>
       <c r="N90">
-        <v>-366.3108727111111</v>
+        <v>-372.5074609111112</v>
       </c>
       <c r="O90">
-        <v>-36.63108727111111</v>
+        <v>-37.25074609111112</v>
       </c>
       <c r="P90">
-        <v>-329.67978544</v>
+        <v>-335.2567148200001</v>
       </c>
       <c r="Q90">
-        <v>-300.7797854400001</v>
+        <v>-306.3567148200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3594094053367725</v>
+        <v>0.3879193512764791</v>
       </c>
       <c r="T90">
-        <v>6.285880286232367</v>
+        <v>6.857323948617129</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03282394409337458</v>
+        <v>0.03245513573277486</v>
       </c>
       <c r="W90">
-        <v>0.2280601139827823</v>
+        <v>0.2281470789942117</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3282394409337458</v>
+        <v>0.3245513573277486</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2457220289452611</v>
+        <v>0.2476220289452611</v>
       </c>
       <c r="C91">
-        <v>-1738.599300462113</v>
+        <v>-1769.534879498769</v>
       </c>
       <c r="D91">
-        <v>494.6316995378871</v>
+        <v>489.9751205012305</v>
       </c>
       <c r="E91">
-        <v>1453.831</v>
+        <v>1480.11</v>
       </c>
       <c r="F91">
-        <v>2338.831</v>
+        <v>2365.11</v>
       </c>
       <c r="G91">
         <v>105.6</v>
@@ -8731,37 +8731,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M91">
-        <v>551.4963498000001</v>
+        <v>557.692938</v>
       </c>
       <c r="N91">
-        <v>-372.5074609111112</v>
+        <v>-378.7040491111111</v>
       </c>
       <c r="O91">
-        <v>-37.25074609111112</v>
+        <v>-37.87040491111112</v>
       </c>
       <c r="P91">
-        <v>-335.2567148200001</v>
+        <v>-340.8336442</v>
       </c>
       <c r="Q91">
-        <v>-306.3567148200001</v>
+        <v>-311.9336442</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3879193512764791</v>
+        <v>0.4221312864041271</v>
       </c>
       <c r="T91">
-        <v>6.857323948617129</v>
+        <v>7.543056343478843</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03245513573277486</v>
+        <v>0.03209452311352181</v>
       </c>
       <c r="W91">
-        <v>0.2281470789942117</v>
+        <v>0.2282321114498316</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3245513573277486</v>
+        <v>0.3209452311352181</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2476220289452611</v>
+        <v>0.2495220289452611</v>
       </c>
       <c r="C92">
-        <v>-1769.534879498769</v>
+        <v>-1800.383599983943</v>
       </c>
       <c r="D92">
-        <v>489.9751205012305</v>
+        <v>485.4054000160568</v>
       </c>
       <c r="E92">
-        <v>1480.11</v>
+        <v>1506.389</v>
       </c>
       <c r="F92">
-        <v>2365.11</v>
+        <v>2391.389</v>
       </c>
       <c r="G92">
         <v>105.6</v>
@@ -8813,37 +8813,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M92">
-        <v>557.692938</v>
+        <v>563.8895262000001</v>
       </c>
       <c r="N92">
-        <v>-378.7040491111111</v>
+        <v>-384.9006373111112</v>
       </c>
       <c r="O92">
-        <v>-37.87040491111112</v>
+        <v>-38.49006373111112</v>
       </c>
       <c r="P92">
-        <v>-340.8336442</v>
+        <v>-346.4105735800001</v>
       </c>
       <c r="Q92">
-        <v>-311.9336442</v>
+        <v>-317.5105735800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4221312864041271</v>
+        <v>0.4639458737823633</v>
       </c>
       <c r="T92">
-        <v>7.543056343478843</v>
+        <v>8.381173714976491</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03209452311352181</v>
+        <v>0.03174183604634025</v>
       </c>
       <c r="W92">
-        <v>0.2282321114498316</v>
+        <v>0.228315275060273</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3209452311352181</v>
+        <v>0.3174183604634025</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2495220289452611</v>
+        <v>0.2514220289452611</v>
       </c>
       <c r="C93">
-        <v>-1800.383599983943</v>
+        <v>-1831.147869703153</v>
       </c>
       <c r="D93">
-        <v>485.4054000160568</v>
+        <v>480.9201302968476</v>
       </c>
       <c r="E93">
-        <v>1506.389</v>
+        <v>1532.668</v>
       </c>
       <c r="F93">
-        <v>2391.389</v>
+        <v>2417.668</v>
       </c>
       <c r="G93">
         <v>105.6</v>
@@ -8895,37 +8895,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M93">
-        <v>563.8895262000001</v>
+        <v>570.0861144</v>
       </c>
       <c r="N93">
-        <v>-384.9006373111112</v>
+        <v>-391.0972255111112</v>
       </c>
       <c r="O93">
-        <v>-38.49006373111112</v>
+        <v>-39.10972255111112</v>
       </c>
       <c r="P93">
-        <v>-346.4105735800001</v>
+        <v>-351.98750296</v>
       </c>
       <c r="Q93">
-        <v>-317.5105735800001</v>
+        <v>-323.0875029600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4639458737823633</v>
+        <v>0.516214108005159</v>
       </c>
       <c r="T93">
-        <v>8.381173714976491</v>
+        <v>9.428820429348557</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03174183604634025</v>
+        <v>0.03139681608931482</v>
       </c>
       <c r="W93">
-        <v>0.228315275060273</v>
+        <v>0.2283966307661396</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3174183604634025</v>
+        <v>0.3139681608931482</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2514220289452611</v>
+        <v>0.2533220289452611</v>
       </c>
       <c r="C94">
-        <v>-1831.147869703153</v>
+        <v>-1861.830008262505</v>
       </c>
       <c r="D94">
-        <v>480.9201302968476</v>
+        <v>476.5169917374948</v>
       </c>
       <c r="E94">
-        <v>1532.668</v>
+        <v>1558.947</v>
       </c>
       <c r="F94">
-        <v>2417.668</v>
+        <v>2443.947</v>
       </c>
       <c r="G94">
         <v>105.6</v>
@@ -8977,37 +8977,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M94">
-        <v>570.0861144</v>
+        <v>576.2827026000001</v>
       </c>
       <c r="N94">
-        <v>-391.0972255111112</v>
+        <v>-397.2938137111112</v>
       </c>
       <c r="O94">
-        <v>-39.10972255111112</v>
+        <v>-39.72938137111112</v>
       </c>
       <c r="P94">
-        <v>-351.98750296</v>
+        <v>-357.5644323400001</v>
       </c>
       <c r="Q94">
-        <v>-323.0875029600001</v>
+        <v>-328.6644323400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.516214108005159</v>
+        <v>0.5834161234344674</v>
       </c>
       <c r="T94">
-        <v>9.428820429348557</v>
+        <v>10.77579477639835</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03139681608931482</v>
+        <v>0.03105921591631143</v>
       </c>
       <c r="W94">
-        <v>0.2283966307661396</v>
+        <v>0.2284762368869338</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3139681608931482</v>
+        <v>0.3105921591631142</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2533220289452611</v>
+        <v>0.2552220289452611</v>
       </c>
       <c r="C95">
-        <v>-1861.830008262505</v>
+        <v>-1892.432251088779</v>
       </c>
       <c r="D95">
-        <v>476.5169917374948</v>
+        <v>472.1937489112213</v>
       </c>
       <c r="E95">
-        <v>1558.947</v>
+        <v>1585.226</v>
       </c>
       <c r="F95">
-        <v>2443.947</v>
+        <v>2470.226</v>
       </c>
       <c r="G95">
         <v>105.6</v>
@@ -9059,37 +9059,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M95">
-        <v>576.2827026000001</v>
+        <v>582.4792908000001</v>
       </c>
       <c r="N95">
-        <v>-397.2938137111112</v>
+        <v>-403.4904019111112</v>
       </c>
       <c r="O95">
-        <v>-39.72938137111112</v>
+        <v>-40.34904019111112</v>
       </c>
       <c r="P95">
-        <v>-357.5644323400001</v>
+        <v>-363.1413617200001</v>
       </c>
       <c r="Q95">
-        <v>-328.6644323400001</v>
+        <v>-334.2413617200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5834161234344674</v>
+        <v>0.6730188106735454</v>
       </c>
       <c r="T95">
-        <v>10.77579477639835</v>
+        <v>12.57176057246475</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03105921591631143</v>
+        <v>0.03072879872571237</v>
       </c>
       <c r="W95">
-        <v>0.2284762368869338</v>
+        <v>0.228554149260477</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3105921591631142</v>
+        <v>0.3072879872571237</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2552220289452611</v>
+        <v>0.2571220289452611</v>
       </c>
       <c r="C96">
-        <v>-1892.432251088779</v>
+        <v>-1922.956753213708</v>
       </c>
       <c r="D96">
-        <v>472.1937489112213</v>
+        <v>467.9482467862927</v>
       </c>
       <c r="E96">
-        <v>1585.226</v>
+        <v>1611.505</v>
       </c>
       <c r="F96">
-        <v>2470.226</v>
+        <v>2496.505</v>
       </c>
       <c r="G96">
         <v>105.6</v>
@@ -9141,37 +9141,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M96">
-        <v>582.4792908000001</v>
+        <v>588.675879</v>
       </c>
       <c r="N96">
-        <v>-403.4904019111112</v>
+        <v>-409.6869901111111</v>
       </c>
       <c r="O96">
-        <v>-40.34904019111112</v>
+        <v>-40.96869901111111</v>
       </c>
       <c r="P96">
-        <v>-363.1413617200001</v>
+        <v>-368.7182911</v>
       </c>
       <c r="Q96">
-        <v>-334.2413617200001</v>
+        <v>-339.8182911</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6730188106735454</v>
+        <v>0.7984625728082549</v>
       </c>
       <c r="T96">
-        <v>12.57176057246475</v>
+        <v>15.0861126869577</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03072879872571237</v>
+        <v>0.03040533768649435</v>
       </c>
       <c r="W96">
-        <v>0.228554149260477</v>
+        <v>0.2286304213735247</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3072879872571237</v>
+        <v>0.3040533768649435</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2571220289452611</v>
+        <v>0.2590220289452611</v>
       </c>
       <c r="C97">
-        <v>-1922.956753213708</v>
+        <v>-1953.405592855943</v>
       </c>
       <c r="D97">
-        <v>467.9482467862927</v>
+        <v>463.7784071440567</v>
       </c>
       <c r="E97">
-        <v>1611.505</v>
+        <v>1637.784</v>
       </c>
       <c r="F97">
-        <v>2496.505</v>
+        <v>2522.784</v>
       </c>
       <c r="G97">
         <v>105.6</v>
@@ -9223,37 +9223,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M97">
-        <v>588.675879</v>
+        <v>594.8724672000001</v>
       </c>
       <c r="N97">
-        <v>-409.6869901111111</v>
+        <v>-415.8835783111112</v>
       </c>
       <c r="O97">
-        <v>-40.96869901111111</v>
+        <v>-41.58835783111113</v>
       </c>
       <c r="P97">
-        <v>-368.7182911</v>
+        <v>-374.2952204800001</v>
       </c>
       <c r="Q97">
-        <v>-339.8182911</v>
+        <v>-345.39522048</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7984625728082549</v>
+        <v>0.9866282160103191</v>
       </c>
       <c r="T97">
-        <v>15.0861126869577</v>
+        <v>18.85764085869714</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03040533768649435</v>
+        <v>0.0300886154189267</v>
       </c>
       <c r="W97">
-        <v>0.2286304213735247</v>
+        <v>0.2287051044842171</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3040533768649435</v>
+        <v>0.300886154189267</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2590220289452611</v>
+        <v>0.2609220289452611</v>
       </c>
       <c r="C98">
-        <v>-1953.405592855943</v>
+        <v>-1983.780774813199</v>
       </c>
       <c r="D98">
-        <v>463.7784071440567</v>
+        <v>459.6822251868016</v>
       </c>
       <c r="E98">
-        <v>1637.784</v>
+        <v>1664.063</v>
       </c>
       <c r="F98">
-        <v>2522.784</v>
+        <v>2549.063</v>
       </c>
       <c r="G98">
         <v>105.6</v>
@@ -9305,37 +9305,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M98">
-        <v>594.8724672000001</v>
+        <v>601.0690554</v>
       </c>
       <c r="N98">
-        <v>-415.8835783111112</v>
+        <v>-422.0801665111111</v>
       </c>
       <c r="O98">
-        <v>-41.58835783111113</v>
+        <v>-42.20801665111112</v>
       </c>
       <c r="P98">
-        <v>-374.2952204800001</v>
+        <v>-379.87214986</v>
       </c>
       <c r="Q98">
-        <v>-345.39522048</v>
+        <v>-350.9721498600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9866282160103165</v>
+        <v>1.300237621347089</v>
       </c>
       <c r="T98">
-        <v>18.85764085869708</v>
+        <v>25.14352114492945</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0300886154189267</v>
+        <v>0.02977842350739137</v>
       </c>
       <c r="W98">
-        <v>0.2287051044842171</v>
+        <v>0.2287782477369571</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.300886154189267</v>
+        <v>0.2977842350739137</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2609220289452611</v>
+        <v>0.2628220289452611</v>
       </c>
       <c r="C99">
-        <v>-1983.780774813199</v>
+        <v>-2014.084233676198</v>
       </c>
       <c r="D99">
-        <v>459.6822251868016</v>
+        <v>455.6577663238019</v>
       </c>
       <c r="E99">
-        <v>1664.063</v>
+        <v>1690.342</v>
       </c>
       <c r="F99">
-        <v>2549.063</v>
+        <v>2575.342</v>
       </c>
       <c r="G99">
         <v>105.6</v>
@@ -9387,37 +9387,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M99">
-        <v>601.0690554</v>
+        <v>607.2656436000001</v>
       </c>
       <c r="N99">
-        <v>-422.0801665111111</v>
+        <v>-428.2767547111112</v>
       </c>
       <c r="O99">
-        <v>-42.20801665111112</v>
+        <v>-42.82767547111112</v>
       </c>
       <c r="P99">
-        <v>-379.87214986</v>
+        <v>-385.4490792400001</v>
       </c>
       <c r="Q99">
-        <v>-350.9721498600001</v>
+        <v>-356.5490792400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.300237621347089</v>
+        <v>1.927456432020634</v>
       </c>
       <c r="T99">
-        <v>25.14352114492945</v>
+        <v>37.71528171739418</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02977842350739137</v>
+        <v>0.02947456204303023</v>
       </c>
       <c r="W99">
-        <v>0.2287782477369571</v>
+        <v>0.2288498982702535</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2977842350739137</v>
+        <v>0.2947456204303023</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2628220289452611</v>
+        <v>0.2647220289452611</v>
       </c>
       <c r="C100">
-        <v>-2014.084233676198</v>
+        <v>-2044.317836875275</v>
       </c>
       <c r="D100">
-        <v>455.6577663238019</v>
+        <v>451.7031631247253</v>
       </c>
       <c r="E100">
-        <v>1690.342</v>
+        <v>1716.621</v>
       </c>
       <c r="F100">
-        <v>2575.342</v>
+        <v>2601.621</v>
       </c>
       <c r="G100">
         <v>105.6</v>
@@ -9469,37 +9469,37 @@
         <v>178.9888888888889</v>
       </c>
       <c r="M100">
-        <v>607.2656436000001</v>
+        <v>613.4622318</v>
       </c>
       <c r="N100">
-        <v>-428.2767547111112</v>
+        <v>-434.4733429111112</v>
       </c>
       <c r="O100">
-        <v>-42.82767547111112</v>
+        <v>-43.44733429111112</v>
       </c>
       <c r="P100">
-        <v>-385.4490792400001</v>
+        <v>-391.02600862</v>
       </c>
       <c r="Q100">
-        <v>-356.5490792400001</v>
+        <v>-362.12600862</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.927456432020634</v>
+        <v>3.809112864041267</v>
       </c>
       <c r="T100">
-        <v>37.71528171739418</v>
+        <v>75.43056343478835</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02947456204303023</v>
+        <v>0.02917683919411074</v>
       </c>
       <c r="W100">
-        <v>0.2288498982702535</v>
+        <v>0.2289201013180287</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2947456204303023</v>
+        <v>0.2917683919411074</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2647220289452611</v>
-      </c>
-      <c r="C101">
-        <v>-2044.317836875275</v>
-      </c>
-      <c r="D101">
-        <v>451.7031631247253</v>
-      </c>
-      <c r="E101">
-        <v>1716.621</v>
-      </c>
-      <c r="F101">
-        <v>2601.621</v>
-      </c>
-      <c r="G101">
-        <v>105.6</v>
-      </c>
-      <c r="H101">
-        <v>1742.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>207.8888888888889</v>
-      </c>
-      <c r="K101">
-        <v>28.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>178.9888888888889</v>
-      </c>
-      <c r="M101">
-        <v>613.4622318</v>
-      </c>
-      <c r="N101">
-        <v>-434.4733429111112</v>
-      </c>
-      <c r="O101">
-        <v>-43.44733429111112</v>
-      </c>
-      <c r="P101">
-        <v>-391.02600862</v>
-      </c>
-      <c r="Q101">
-        <v>-362.12600862</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.809112864041267</v>
-      </c>
-      <c r="T101">
-        <v>75.43056343478835</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02917683919411074</v>
-      </c>
-      <c r="W101">
-        <v>0.2289201013180287</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2917683919411074</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
